--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_chemical_basic.xlsx
@@ -1133,43 +1133,43 @@
         <v>137400</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>201.840642699388</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0951388400702988</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>2706.7</v>
       </c>
       <c r="L2">
-        <v>2706.7</v>
+        <v>2678.51976420848</v>
       </c>
       <c r="M2">
         <v>2386.6</v>
       </c>
       <c r="N2">
-        <v>2386.6</v>
+        <v>2385.48676420848</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>27.067</v>
       </c>
       <c r="Q2">
         <v>0.0922505993377119</v>
       </c>
       <c r="R2">
-        <v>0.0922505993377119</v>
+        <v>0.09229559933771191</v>
       </c>
       <c r="S2">
         <v>0.0612366166625341</v>
@@ -1191,13 +1191,13 @@
         <v>0.0922505993377119</v>
       </c>
       <c r="X2">
-        <v>0.0922505993377119</v>
+        <v>0.0927197973108201</v>
       </c>
       <c r="Y2">
         <v>0.9054086395470869</v>
       </c>
       <c r="Z2">
-        <v>0.9054086395470869</v>
+        <v>0.914554181360694</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09225059933771193</v>
+        <v>0.09229559933771195</v>
       </c>
       <c r="C2">
-        <v>2706.7</v>
+        <v>2678.519764208478</v>
       </c>
       <c r="D2">
-        <v>2386.6</v>
+        <v>2385.486764208478</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>27.067</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27.067</v>
       </c>
       <c r="G2">
         <v>320.1</v>
@@ -1451,28 +1451,28 @@
         <v>274.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.3614701</v>
       </c>
       <c r="N2">
-        <v>274.8</v>
+        <v>273.4385299</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>274.8</v>
+        <v>273.4385299</v>
       </c>
       <c r="Q2">
-        <v>284.5</v>
+        <v>283.1385299</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09225059933771193</v>
+        <v>0.09271979731082014</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9145541813606937</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>201.840642699388</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09229559933771195</v>
+        <v>0.09234059933771194</v>
       </c>
       <c r="C3">
-        <v>2678.519764208478</v>
+        <v>2650.340566476225</v>
       </c>
       <c r="D3">
-        <v>2385.486764208478</v>
+        <v>2384.374566476225</v>
       </c>
       <c r="E3">
-        <v>27.067</v>
+        <v>54.134</v>
       </c>
       <c r="F3">
-        <v>27.067</v>
+        <v>54.134</v>
       </c>
       <c r="G3">
         <v>320.1</v>
@@ -1533,28 +1533,28 @@
         <v>274.8</v>
       </c>
       <c r="M3">
-        <v>1.3614701</v>
+        <v>2.7229402</v>
       </c>
       <c r="N3">
-        <v>273.4385299</v>
+        <v>272.0770598</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>273.4385299</v>
+        <v>272.0770598</v>
       </c>
       <c r="Q3">
-        <v>283.1385299</v>
+        <v>281.7770598</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09271979731082014</v>
+        <v>0.09319857075276727</v>
       </c>
       <c r="T3">
-        <v>0.9145541813606937</v>
+        <v>0.9238863668847823</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>201.840642699388</v>
+        <v>100.920321349694</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09234059933771194</v>
+        <v>0.09238559933771191</v>
       </c>
       <c r="C4">
-        <v>2650.340566476225</v>
+        <v>2622.162405351979</v>
       </c>
       <c r="D4">
-        <v>2384.374566476225</v>
+        <v>2383.263405351979</v>
       </c>
       <c r="E4">
-        <v>54.134</v>
+        <v>81.20099999999999</v>
       </c>
       <c r="F4">
-        <v>54.134</v>
+        <v>81.20099999999999</v>
       </c>
       <c r="G4">
         <v>320.1</v>
@@ -1615,28 +1615,28 @@
         <v>274.8</v>
       </c>
       <c r="M4">
-        <v>2.7229402</v>
+        <v>4.084410299999999</v>
       </c>
       <c r="N4">
-        <v>272.0770598</v>
+        <v>270.7155897</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>272.0770598</v>
+        <v>270.7155897</v>
       </c>
       <c r="Q4">
-        <v>281.7770598</v>
+        <v>280.4155897</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09319857075276727</v>
+        <v>0.09368721581207415</v>
       </c>
       <c r="T4">
-        <v>0.9238863668847823</v>
+        <v>0.9334109686052439</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>100.920321349694</v>
+        <v>67.28021423312934</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09238559933771191</v>
+        <v>0.09243059933771193</v>
       </c>
       <c r="C5">
-        <v>2622.162405351979</v>
+        <v>2593.985279387179</v>
       </c>
       <c r="D5">
-        <v>2383.263405351979</v>
+        <v>2382.153279387179</v>
       </c>
       <c r="E5">
-        <v>81.20099999999999</v>
+        <v>108.268</v>
       </c>
       <c r="F5">
-        <v>81.20099999999999</v>
+        <v>108.268</v>
       </c>
       <c r="G5">
         <v>320.1</v>
@@ -1697,28 +1697,28 @@
         <v>274.8</v>
       </c>
       <c r="M5">
-        <v>4.084410299999999</v>
+        <v>5.4458804</v>
       </c>
       <c r="N5">
-        <v>270.7155897</v>
+        <v>269.3541196</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>270.7155897</v>
+        <v>269.3541196</v>
       </c>
       <c r="Q5">
-        <v>280.4155897</v>
+        <v>279.0541196</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09368721581207415</v>
+        <v>0.09418604097678326</v>
       </c>
       <c r="T5">
-        <v>0.9334109686052439</v>
+        <v>0.9431339995282153</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.28021423312934</v>
+        <v>50.46016067484699</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09243059933771193</v>
+        <v>0.09247559933771193</v>
       </c>
       <c r="C6">
-        <v>2593.985279387179</v>
+        <v>2565.809187135966</v>
       </c>
       <c r="D6">
-        <v>2382.153279387179</v>
+        <v>2381.044187135966</v>
       </c>
       <c r="E6">
-        <v>108.268</v>
+        <v>135.335</v>
       </c>
       <c r="F6">
-        <v>108.268</v>
+        <v>135.335</v>
       </c>
       <c r="G6">
         <v>320.1</v>
@@ -1779,28 +1779,28 @@
         <v>274.8</v>
       </c>
       <c r="M6">
-        <v>5.4458804</v>
+        <v>6.8073505</v>
       </c>
       <c r="N6">
-        <v>269.3541196</v>
+        <v>267.9926495</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>269.3541196</v>
+        <v>267.9926495</v>
       </c>
       <c r="Q6">
-        <v>279.0541196</v>
+        <v>277.6926495</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09418604097678326</v>
+        <v>0.0946953677239073</v>
       </c>
       <c r="T6">
-        <v>0.9431339995282153</v>
+        <v>0.9530617258390385</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.46016067484699</v>
+        <v>40.3681285398776</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09247559933771193</v>
+        <v>0.09252059933771194</v>
       </c>
       <c r="C7">
-        <v>2565.809187135966</v>
+        <v>2537.634127155171</v>
       </c>
       <c r="D7">
-        <v>2381.044187135966</v>
+        <v>2379.936127155171</v>
       </c>
       <c r="E7">
-        <v>135.335</v>
+        <v>162.402</v>
       </c>
       <c r="F7">
-        <v>135.335</v>
+        <v>162.402</v>
       </c>
       <c r="G7">
         <v>320.1</v>
@@ -1861,28 +1861,28 @@
         <v>274.8</v>
       </c>
       <c r="M7">
-        <v>6.8073505</v>
+        <v>8.1688206</v>
       </c>
       <c r="N7">
-        <v>267.9926495</v>
+        <v>266.6311794</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>267.9926495</v>
+        <v>266.6311794</v>
       </c>
       <c r="Q7">
-        <v>277.6926495</v>
+        <v>276.3311794</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0946953677239073</v>
+        <v>0.09521553121033184</v>
       </c>
       <c r="T7">
-        <v>0.9530617258390385</v>
+        <v>0.9632006803692411</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.3681285398776</v>
+        <v>33.64010711656466</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09252059933771192</v>
+        <v>0.09256559933771194</v>
       </c>
       <c r="C8">
-        <v>2537.634127155171</v>
+        <v>2509.46009800431</v>
       </c>
       <c r="D8">
-        <v>2379.936127155172</v>
+        <v>2378.82909800431</v>
       </c>
       <c r="E8">
-        <v>162.402</v>
+        <v>189.469</v>
       </c>
       <c r="F8">
-        <v>162.402</v>
+        <v>189.469</v>
       </c>
       <c r="G8">
         <v>320.1</v>
@@ -1943,28 +1943,28 @@
         <v>274.8</v>
       </c>
       <c r="M8">
-        <v>8.168820599999998</v>
+        <v>9.530290699999998</v>
       </c>
       <c r="N8">
-        <v>266.6311794</v>
+        <v>265.2697093</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>266.6311794</v>
+        <v>265.2697093</v>
       </c>
       <c r="Q8">
-        <v>276.3311794</v>
+        <v>274.9697093</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09521553121033184</v>
+        <v>0.0957468810082924</v>
       </c>
       <c r="T8">
-        <v>0.9632006803692411</v>
+        <v>0.9735576769323512</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.64010711656467</v>
+        <v>28.834377528484</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09256559933771193</v>
+        <v>0.09261059933771193</v>
       </c>
       <c r="C9">
-        <v>2509.46009800431</v>
+        <v>2481.287098245576</v>
       </c>
       <c r="D9">
-        <v>2378.82909800431</v>
+        <v>2377.723098245576</v>
       </c>
       <c r="E9">
-        <v>189.469</v>
+        <v>216.536</v>
       </c>
       <c r="F9">
-        <v>189.469</v>
+        <v>216.536</v>
       </c>
       <c r="G9">
         <v>320.1</v>
@@ -2025,28 +2025,28 @@
         <v>274.8</v>
       </c>
       <c r="M9">
-        <v>9.5302907</v>
+        <v>10.8917608</v>
       </c>
       <c r="N9">
-        <v>265.2697093</v>
+        <v>263.9082392</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>265.2697093</v>
+        <v>263.9082392</v>
       </c>
       <c r="Q9">
-        <v>274.9697093</v>
+        <v>273.6082392</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0957468810082924</v>
+        <v>0.09628978188881732</v>
       </c>
       <c r="T9">
-        <v>0.9735576769323512</v>
+        <v>0.9841398255946593</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.83437752848399</v>
+        <v>25.2300803374235</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09261059933771193</v>
+        <v>0.09265559933771195</v>
       </c>
       <c r="C10">
-        <v>2481.287098245576</v>
+        <v>2453.115126443838</v>
       </c>
       <c r="D10">
-        <v>2377.723098245576</v>
+        <v>2376.618126443838</v>
       </c>
       <c r="E10">
-        <v>216.536</v>
+        <v>243.603</v>
       </c>
       <c r="F10">
-        <v>216.536</v>
+        <v>243.603</v>
       </c>
       <c r="G10">
         <v>320.1</v>
@@ -2107,28 +2107,28 @@
         <v>274.8</v>
       </c>
       <c r="M10">
-        <v>10.8917608</v>
+        <v>12.2532309</v>
       </c>
       <c r="N10">
-        <v>263.9082392</v>
+        <v>262.5467691</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>263.9082392</v>
+        <v>262.5467691</v>
       </c>
       <c r="Q10">
-        <v>273.6082392</v>
+        <v>272.2467691</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09628978188881732</v>
+        <v>0.09684461465682631</v>
       </c>
       <c r="T10">
-        <v>0.9841398255946593</v>
+        <v>0.9949545489528425</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.2300803374235</v>
+        <v>22.42673807770978</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09265559933771195</v>
+        <v>0.09270059933771194</v>
       </c>
       <c r="C11">
-        <v>2453.115126443838</v>
+        <v>2424.944181166629</v>
       </c>
       <c r="D11">
-        <v>2376.618126443838</v>
+        <v>2375.514181166629</v>
       </c>
       <c r="E11">
-        <v>243.603</v>
+        <v>270.67</v>
       </c>
       <c r="F11">
-        <v>243.603</v>
+        <v>270.67</v>
       </c>
       <c r="G11">
         <v>320.1</v>
@@ -2189,28 +2189,28 @@
         <v>274.8</v>
       </c>
       <c r="M11">
-        <v>12.2532309</v>
+        <v>13.614701</v>
       </c>
       <c r="N11">
-        <v>262.5467691</v>
+        <v>261.185299</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>262.5467691</v>
+        <v>261.185299</v>
       </c>
       <c r="Q11">
-        <v>272.2467691</v>
+        <v>270.885299</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09684461465682631</v>
+        <v>0.09741177704190215</v>
       </c>
       <c r="T11">
-        <v>0.9949545489528425</v>
+        <v>1.006009599496763</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.42673807770978</v>
+        <v>20.1840642699388</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09270059933771194</v>
+        <v>0.09274559933771194</v>
       </c>
       <c r="C12">
-        <v>2424.944181166629</v>
+        <v>2396.774260984144</v>
       </c>
       <c r="D12">
-        <v>2375.514181166629</v>
+        <v>2374.411260984144</v>
       </c>
       <c r="E12">
-        <v>270.67</v>
+        <v>297.737</v>
       </c>
       <c r="F12">
-        <v>270.67</v>
+        <v>297.737</v>
       </c>
       <c r="G12">
         <v>320.1</v>
@@ -2271,28 +2271,28 @@
         <v>274.8</v>
       </c>
       <c r="M12">
-        <v>13.614701</v>
+        <v>14.9761711</v>
       </c>
       <c r="N12">
-        <v>261.185299</v>
+        <v>259.8238289</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>261.185299</v>
+        <v>259.8238289</v>
       </c>
       <c r="Q12">
-        <v>270.885299</v>
+        <v>269.5238289</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09741177704190215</v>
+        <v>0.09799168464911454</v>
       </c>
       <c r="T12">
-        <v>1.006009599496763</v>
+        <v>1.017313078142794</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.18406426993879</v>
+        <v>18.349149336308</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09274559933771194</v>
+        <v>0.09279059933771193</v>
       </c>
       <c r="C13">
-        <v>2396.774260984144</v>
+        <v>2368.605364469232</v>
       </c>
       <c r="D13">
-        <v>2374.411260984144</v>
+        <v>2373.309364469232</v>
       </c>
       <c r="E13">
-        <v>297.737</v>
+        <v>324.804</v>
       </c>
       <c r="F13">
-        <v>297.737</v>
+        <v>324.804</v>
       </c>
       <c r="G13">
         <v>320.1</v>
@@ -2353,28 +2353,28 @@
         <v>274.8</v>
       </c>
       <c r="M13">
-        <v>14.9761711</v>
+        <v>16.3376412</v>
       </c>
       <c r="N13">
-        <v>259.8238289</v>
+        <v>258.4623588</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>259.8238289</v>
+        <v>258.4623588</v>
       </c>
       <c r="Q13">
-        <v>269.5238289</v>
+        <v>268.1623588</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09799168464911454</v>
+        <v>0.09858477197467265</v>
       </c>
       <c r="T13">
-        <v>1.017313078142794</v>
+        <v>1.02887345403078</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.349149336308</v>
+        <v>16.82005355828233</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09279059933771193</v>
+        <v>0.09283559933771193</v>
       </c>
       <c r="C14">
-        <v>2368.605364469232</v>
+        <v>2340.437490197387</v>
       </c>
       <c r="D14">
-        <v>2373.309364469232</v>
+        <v>2372.208490197387</v>
       </c>
       <c r="E14">
-        <v>324.804</v>
+        <v>351.871</v>
       </c>
       <c r="F14">
-        <v>324.804</v>
+        <v>351.871</v>
       </c>
       <c r="G14">
         <v>320.1</v>
@@ -2435,28 +2435,28 @@
         <v>274.8</v>
       </c>
       <c r="M14">
-        <v>16.3376412</v>
+        <v>17.6991113</v>
       </c>
       <c r="N14">
-        <v>258.4623588</v>
+        <v>257.1008887</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>258.4623588</v>
+        <v>257.1008887</v>
       </c>
       <c r="Q14">
-        <v>268.1623588</v>
+        <v>266.8008887</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09858477197467265</v>
+        <v>0.0991914934916229</v>
       </c>
       <c r="T14">
-        <v>1.02887345403078</v>
+        <v>1.040699585686306</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.82005355828233</v>
+        <v>15.52620328456831</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09283559933771193</v>
+        <v>0.09288059933771194</v>
       </c>
       <c r="C15">
-        <v>2340.437490197387</v>
+        <v>2312.270636746749</v>
       </c>
       <c r="D15">
-        <v>2372.208490197387</v>
+        <v>2371.108636746749</v>
       </c>
       <c r="E15">
-        <v>351.871</v>
+        <v>378.938</v>
       </c>
       <c r="F15">
-        <v>351.871</v>
+        <v>378.938</v>
       </c>
       <c r="G15">
         <v>320.1</v>
@@ -2517,28 +2517,28 @@
         <v>274.8</v>
       </c>
       <c r="M15">
-        <v>17.6991113</v>
+        <v>19.0605814</v>
       </c>
       <c r="N15">
-        <v>257.1008887</v>
+        <v>255.7394186</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>257.1008887</v>
+        <v>255.7394186</v>
       </c>
       <c r="Q15">
-        <v>266.8008887</v>
+        <v>265.4394186</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0991914934916229</v>
+        <v>0.09981232481129294</v>
       </c>
       <c r="T15">
-        <v>1.040699585686306</v>
+        <v>1.052800743659403</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.52620328456831</v>
+        <v>14.417188764242</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09288059933771194</v>
+        <v>0.09292559933771193</v>
       </c>
       <c r="C16">
-        <v>2312.270636746749</v>
+        <v>2284.104802698092</v>
       </c>
       <c r="D16">
-        <v>2371.108636746749</v>
+        <v>2370.009802698092</v>
       </c>
       <c r="E16">
-        <v>378.938</v>
+        <v>406.0050000000001</v>
       </c>
       <c r="F16">
-        <v>378.938</v>
+        <v>406.0050000000001</v>
       </c>
       <c r="G16">
         <v>320.1</v>
@@ -2599,28 +2599,28 @@
         <v>274.8</v>
       </c>
       <c r="M16">
-        <v>19.0605814</v>
+        <v>20.4220515</v>
       </c>
       <c r="N16">
-        <v>255.7394186</v>
+        <v>254.3779485</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>255.7394186</v>
+        <v>254.3779485</v>
       </c>
       <c r="Q16">
-        <v>265.4394186</v>
+        <v>264.0779485</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09981232481129294</v>
+        <v>0.1004477639267199</v>
       </c>
       <c r="T16">
-        <v>1.052800743659403</v>
+        <v>1.065186634761278</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.417188764242</v>
+        <v>13.45604284662586</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09292559933771193</v>
+        <v>0.09321059933771193</v>
       </c>
       <c r="C17">
-        <v>2284.104802698092</v>
+        <v>2250.102102015226</v>
       </c>
       <c r="D17">
-        <v>2370.009802698092</v>
+        <v>2363.074102015226</v>
       </c>
       <c r="E17">
-        <v>406.0049999999999</v>
+        <v>433.072</v>
       </c>
       <c r="F17">
-        <v>406.0049999999999</v>
+        <v>433.072</v>
       </c>
       <c r="G17">
         <v>320.1</v>
@@ -2681,45 +2681,45 @@
         <v>274.8</v>
       </c>
       <c r="M17">
-        <v>20.42205149999999</v>
+        <v>22.4331296</v>
       </c>
       <c r="N17">
-        <v>254.3779485</v>
+        <v>252.3668704</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>254.3779485</v>
+        <v>252.3668704</v>
       </c>
       <c r="Q17">
-        <v>264.0779485</v>
+        <v>262.0668704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1004477639267199</v>
+        <v>0.1010983325448952</v>
       </c>
       <c r="T17">
-        <v>1.065186634761278</v>
+        <v>1.077867428032246</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.45604284662587</v>
+        <v>12.24973977772589</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09321059933771193</v>
+        <v>0.09327059933771194</v>
       </c>
       <c r="C18">
-        <v>2250.102102015226</v>
+        <v>2221.580123945251</v>
       </c>
       <c r="D18">
-        <v>2363.074102015226</v>
+        <v>2361.619123945251</v>
       </c>
       <c r="E18">
-        <v>433.072</v>
+        <v>460.139</v>
       </c>
       <c r="F18">
-        <v>433.072</v>
+        <v>460.139</v>
       </c>
       <c r="G18">
         <v>320.1</v>
@@ -2763,28 +2763,28 @@
         <v>274.8</v>
       </c>
       <c r="M18">
-        <v>22.4331296</v>
+        <v>23.8352002</v>
       </c>
       <c r="N18">
-        <v>252.3668704</v>
+        <v>250.9647998</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>252.3668704</v>
+        <v>250.9647998</v>
       </c>
       <c r="Q18">
-        <v>262.0668704</v>
+        <v>260.6647998</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1010983325448952</v>
+        <v>0.1017645775153156</v>
       </c>
       <c r="T18">
-        <v>1.077867428032246</v>
+        <v>1.090853782586851</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.24973977772589</v>
+        <v>11.52916684962436</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09327059933771194</v>
+        <v>0.09333059933771193</v>
       </c>
       <c r="C19">
-        <v>2221.580123945251</v>
+        <v>2193.059936473837</v>
       </c>
       <c r="D19">
-        <v>2361.619123945251</v>
+        <v>2360.165936473838</v>
       </c>
       <c r="E19">
-        <v>460.139</v>
+        <v>487.206</v>
       </c>
       <c r="F19">
-        <v>460.139</v>
+        <v>487.206</v>
       </c>
       <c r="G19">
         <v>320.1</v>
@@ -2845,28 +2845,28 @@
         <v>274.8</v>
       </c>
       <c r="M19">
-        <v>23.8352002</v>
+        <v>25.2372708</v>
       </c>
       <c r="N19">
-        <v>250.9647998</v>
+        <v>249.5627292</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>250.9647998</v>
+        <v>249.5627292</v>
       </c>
       <c r="Q19">
-        <v>260.6647998</v>
+        <v>259.2627292</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1017645775153156</v>
+        <v>0.1024470723630633</v>
       </c>
       <c r="T19">
-        <v>1.090853782586851</v>
+        <v>1.104156877496447</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.52916684962436</v>
+        <v>10.88865758020079</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09333059933771194</v>
+        <v>0.09339059933771193</v>
       </c>
       <c r="C20">
-        <v>2193.059936473837</v>
+        <v>2164.541536297562</v>
       </c>
       <c r="D20">
-        <v>2360.165936473837</v>
+        <v>2358.714536297562</v>
       </c>
       <c r="E20">
-        <v>487.206</v>
+        <v>514.273</v>
       </c>
       <c r="F20">
-        <v>487.206</v>
+        <v>514.273</v>
       </c>
       <c r="G20">
         <v>320.1</v>
@@ -2927,28 +2927,28 @@
         <v>274.8</v>
       </c>
       <c r="M20">
-        <v>25.2372708</v>
+        <v>26.6393414</v>
       </c>
       <c r="N20">
-        <v>249.5627292</v>
+        <v>248.1606586</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>249.5627292</v>
+        <v>248.1606586</v>
       </c>
       <c r="Q20">
-        <v>259.2627292</v>
+        <v>257.8606586</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1024470723630633</v>
+        <v>0.1031464189354468</v>
       </c>
       <c r="T20">
-        <v>1.104156877496447</v>
+        <v>1.117788443885292</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.88865758020079</v>
+        <v>10.31557033913759</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09339059933771193</v>
+        <v>0.09379059933771194</v>
       </c>
       <c r="C21">
-        <v>2164.541536297562</v>
+        <v>2127.843968004158</v>
       </c>
       <c r="D21">
-        <v>2358.714536297562</v>
+        <v>2349.083968004158</v>
       </c>
       <c r="E21">
-        <v>514.273</v>
+        <v>541.34</v>
       </c>
       <c r="F21">
-        <v>514.273</v>
+        <v>541.34</v>
       </c>
       <c r="G21">
         <v>320.1</v>
@@ -3009,45 +3009,45 @@
         <v>274.8</v>
       </c>
       <c r="M21">
-        <v>26.6393414</v>
+        <v>28.96169</v>
       </c>
       <c r="N21">
-        <v>248.1606586</v>
+        <v>245.83831</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>248.1606586</v>
+        <v>245.83831</v>
       </c>
       <c r="Q21">
-        <v>257.8606586</v>
+        <v>255.53831</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1031464189354468</v>
+        <v>0.1038632491721399</v>
       </c>
       <c r="T21">
-        <v>1.117788443885292</v>
+        <v>1.131760799433858</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.31557033913759</v>
+        <v>9.488396568017958</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09379059933771194</v>
+        <v>0.09386759933771194</v>
       </c>
       <c r="C22">
-        <v>2127.843968004158</v>
+        <v>2098.932102980918</v>
       </c>
       <c r="D22">
-        <v>2349.083968004158</v>
+        <v>2347.239102980918</v>
       </c>
       <c r="E22">
-        <v>541.34</v>
+        <v>568.407</v>
       </c>
       <c r="F22">
-        <v>541.34</v>
+        <v>568.407</v>
       </c>
       <c r="G22">
         <v>320.1</v>
@@ -3091,28 +3091,28 @@
         <v>274.8</v>
       </c>
       <c r="M22">
-        <v>28.96169</v>
+        <v>30.4097745</v>
       </c>
       <c r="N22">
-        <v>245.83831</v>
+        <v>244.3902255</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>245.83831</v>
+        <v>244.3902255</v>
       </c>
       <c r="Q22">
-        <v>255.53831</v>
+        <v>254.0902255</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1038632491721399</v>
+        <v>0.1045982270097619</v>
       </c>
       <c r="T22">
-        <v>1.131760799433858</v>
+        <v>1.146086885502641</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.488396568017958</v>
+        <v>9.036568160017103</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09386759933771194</v>
+        <v>0.09394459933771193</v>
       </c>
       <c r="C23">
-        <v>2098.932102980918</v>
+        <v>2070.023133431931</v>
       </c>
       <c r="D23">
-        <v>2347.239102980918</v>
+        <v>2345.397133431931</v>
       </c>
       <c r="E23">
-        <v>568.4069999999999</v>
+        <v>595.4739999999999</v>
       </c>
       <c r="F23">
-        <v>568.4069999999999</v>
+        <v>595.4739999999999</v>
       </c>
       <c r="G23">
         <v>320.1</v>
@@ -3173,28 +3173,28 @@
         <v>274.8</v>
       </c>
       <c r="M23">
-        <v>30.40977449999999</v>
+        <v>31.85785899999999</v>
       </c>
       <c r="N23">
-        <v>244.3902255</v>
+        <v>242.942141</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>244.3902255</v>
+        <v>242.942141</v>
       </c>
       <c r="Q23">
-        <v>254.0902255</v>
+        <v>252.642141</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1045982270097619</v>
+        <v>0.105352050432964</v>
       </c>
       <c r="T23">
-        <v>1.146086885502641</v>
+        <v>1.160780307111649</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.036568160017104</v>
+        <v>8.625815061834508</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09394459933771193</v>
+        <v>0.09402159933771191</v>
       </c>
       <c r="C24">
-        <v>2070.023133431931</v>
+        <v>2041.117052545969</v>
       </c>
       <c r="D24">
-        <v>2345.397133431931</v>
+        <v>2343.55805254597</v>
       </c>
       <c r="E24">
-        <v>595.4739999999999</v>
+        <v>622.5409999999999</v>
       </c>
       <c r="F24">
-        <v>595.4739999999999</v>
+        <v>622.5409999999999</v>
       </c>
       <c r="G24">
         <v>320.1</v>
@@ -3255,28 +3255,28 @@
         <v>274.8</v>
       </c>
       <c r="M24">
-        <v>31.85785899999999</v>
+        <v>33.3059435</v>
       </c>
       <c r="N24">
-        <v>242.942141</v>
+        <v>241.4940565</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>242.942141</v>
+        <v>241.4940565</v>
       </c>
       <c r="Q24">
-        <v>252.642141</v>
+        <v>251.1940565</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.105352050432964</v>
+        <v>0.1061254536853402</v>
       </c>
       <c r="T24">
-        <v>1.160780307111649</v>
+        <v>1.175855376035177</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.625815061834508</v>
+        <v>8.250779624363442</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09402159933771191</v>
+        <v>0.09409859933771193</v>
       </c>
       <c r="C25">
-        <v>2041.117052545969</v>
+        <v>2012.213853533152</v>
       </c>
       <c r="D25">
-        <v>2343.55805254597</v>
+        <v>2341.721853533153</v>
       </c>
       <c r="E25">
-        <v>622.5409999999999</v>
+        <v>649.6080000000001</v>
       </c>
       <c r="F25">
-        <v>622.5409999999999</v>
+        <v>649.6080000000001</v>
       </c>
       <c r="G25">
         <v>320.1</v>
@@ -3337,28 +3337,28 @@
         <v>274.8</v>
       </c>
       <c r="M25">
-        <v>33.3059435</v>
+        <v>34.75402800000001</v>
       </c>
       <c r="N25">
-        <v>241.4940565</v>
+        <v>240.045972</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>241.4940565</v>
+        <v>240.045972</v>
       </c>
       <c r="Q25">
-        <v>251.1940565</v>
+        <v>249.745972</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1061254536853402</v>
+        <v>0.1069192096548841</v>
       </c>
       <c r="T25">
-        <v>1.175855376035177</v>
+        <v>1.191327157298798</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.250779624363442</v>
+        <v>7.906997140014964</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09409859933771193</v>
+        <v>0.09437559933771193</v>
       </c>
       <c r="C26">
-        <v>2012.213853533153</v>
+        <v>1978.565033443521</v>
       </c>
       <c r="D26">
-        <v>2341.721853533153</v>
+        <v>2335.140033443521</v>
       </c>
       <c r="E26">
-        <v>649.6079999999999</v>
+        <v>676.675</v>
       </c>
       <c r="F26">
-        <v>649.6079999999999</v>
+        <v>676.675</v>
       </c>
       <c r="G26">
         <v>320.1</v>
@@ -3419,45 +3419,45 @@
         <v>274.8</v>
       </c>
       <c r="M26">
-        <v>34.754028</v>
+        <v>36.7434525</v>
       </c>
       <c r="N26">
-        <v>240.045972</v>
+        <v>238.0565475</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>240.045972</v>
+        <v>238.0565475</v>
       </c>
       <c r="Q26">
-        <v>249.745972</v>
+        <v>247.7565475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1069192096548841</v>
+        <v>0.1077341324502826</v>
       </c>
       <c r="T26">
-        <v>1.191327157298798</v>
+        <v>1.207211519396115</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.906997140014965</v>
+        <v>7.478883482710288</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09437559933771193</v>
+        <v>0.09446059933771193</v>
       </c>
       <c r="C27">
-        <v>1978.565033443521</v>
+        <v>1949.485753611579</v>
       </c>
       <c r="D27">
-        <v>2335.140033443521</v>
+        <v>2333.127753611579</v>
       </c>
       <c r="E27">
-        <v>676.675</v>
+        <v>703.742</v>
       </c>
       <c r="F27">
-        <v>676.675</v>
+        <v>703.742</v>
       </c>
       <c r="G27">
         <v>320.1</v>
@@ -3501,28 +3501,28 @@
         <v>274.8</v>
       </c>
       <c r="M27">
-        <v>36.7434525</v>
+        <v>38.2131906</v>
       </c>
       <c r="N27">
-        <v>238.0565475</v>
+        <v>236.5868094</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>238.0565475</v>
+        <v>236.5868094</v>
       </c>
       <c r="Q27">
-        <v>247.7565475</v>
+        <v>246.2868094</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1077341324502826</v>
+        <v>0.1085710801860972</v>
       </c>
       <c r="T27">
-        <v>1.207211519396115</v>
+        <v>1.223525188577144</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.478883482710288</v>
+        <v>7.191234117990661</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09446059933771193</v>
+        <v>0.09454559933771195</v>
       </c>
       <c r="C28">
-        <v>1949.485753611579</v>
+        <v>1920.409938911197</v>
       </c>
       <c r="D28">
-        <v>2333.127753611579</v>
+        <v>2331.118938911197</v>
       </c>
       <c r="E28">
-        <v>703.742</v>
+        <v>730.809</v>
       </c>
       <c r="F28">
-        <v>703.742</v>
+        <v>730.809</v>
       </c>
       <c r="G28">
         <v>320.1</v>
@@ -3583,28 +3583,28 @@
         <v>274.8</v>
       </c>
       <c r="M28">
-        <v>38.2131906</v>
+        <v>39.6829287</v>
       </c>
       <c r="N28">
-        <v>236.5868094</v>
+        <v>235.1170713</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>236.5868094</v>
+        <v>235.1170713</v>
       </c>
       <c r="Q28">
-        <v>246.2868094</v>
+        <v>244.8170713</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1085710801860972</v>
+        <v>0.1094309579968657</v>
       </c>
       <c r="T28">
-        <v>1.223525188577144</v>
+        <v>1.240285807598749</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.191234117990661</v>
+        <v>6.924892113620637</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09454559933771195</v>
+        <v>0.09463059933771192</v>
       </c>
       <c r="C29">
-        <v>1920.409938911197</v>
+        <v>1891.33758039968</v>
       </c>
       <c r="D29">
-        <v>2331.118938911197</v>
+        <v>2329.11358039968</v>
       </c>
       <c r="E29">
-        <v>730.809</v>
+        <v>757.876</v>
       </c>
       <c r="F29">
-        <v>730.809</v>
+        <v>757.876</v>
       </c>
       <c r="G29">
         <v>320.1</v>
@@ -3665,28 +3665,28 @@
         <v>274.8</v>
       </c>
       <c r="M29">
-        <v>39.6829287</v>
+        <v>41.1526668</v>
       </c>
       <c r="N29">
-        <v>235.1170713</v>
+        <v>233.6473332</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>235.1170713</v>
+        <v>233.6473332</v>
       </c>
       <c r="Q29">
-        <v>244.8170713</v>
+        <v>243.3473332</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1094309579968657</v>
+        <v>0.1103147213023777</v>
       </c>
       <c r="T29">
-        <v>1.240285807598749</v>
+        <v>1.257511999370954</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.924892113620637</v>
+        <v>6.677574538134185</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09463059933771192</v>
+        <v>0.09471559933771193</v>
       </c>
       <c r="C30">
-        <v>1891.33758039968</v>
+        <v>1862.268669165072</v>
       </c>
       <c r="D30">
-        <v>2329.11358039968</v>
+        <v>2327.111669165072</v>
       </c>
       <c r="E30">
-        <v>757.876</v>
+        <v>784.9430000000001</v>
       </c>
       <c r="F30">
-        <v>757.876</v>
+        <v>784.9430000000001</v>
       </c>
       <c r="G30">
         <v>320.1</v>
@@ -3747,28 +3747,28 @@
         <v>274.8</v>
       </c>
       <c r="M30">
-        <v>41.1526668</v>
+        <v>42.62240490000001</v>
       </c>
       <c r="N30">
-        <v>233.6473332</v>
+        <v>232.1775951</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>233.6473332</v>
+        <v>232.1775951</v>
       </c>
       <c r="Q30">
-        <v>243.3473332</v>
+        <v>241.8775951</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1103147213023777</v>
+        <v>0.11122337934889</v>
       </c>
       <c r="T30">
-        <v>1.257511999370954</v>
+        <v>1.275223435981812</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.677574538134185</v>
+        <v>6.44731334716404</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09471559933771193</v>
+        <v>0.09480059933771193</v>
       </c>
       <c r="C31">
-        <v>1862.268669165072</v>
+        <v>1833.203196326035</v>
       </c>
       <c r="D31">
-        <v>2327.111669165072</v>
+        <v>2325.113196326035</v>
       </c>
       <c r="E31">
-        <v>784.9429999999999</v>
+        <v>812.0099999999999</v>
       </c>
       <c r="F31">
-        <v>784.9429999999999</v>
+        <v>812.0099999999999</v>
       </c>
       <c r="G31">
         <v>320.1</v>
@@ -3829,28 +3829,28 @@
         <v>274.8</v>
       </c>
       <c r="M31">
-        <v>42.62240489999999</v>
+        <v>44.09214299999999</v>
       </c>
       <c r="N31">
-        <v>232.1775951</v>
+        <v>230.707857</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>232.1775951</v>
+        <v>230.707857</v>
       </c>
       <c r="Q31">
-        <v>241.8775951</v>
+        <v>240.407857</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.11122337934889</v>
+        <v>0.1121579990538742</v>
       </c>
       <c r="T31">
-        <v>1.275223435981812</v>
+        <v>1.293440913638695</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.447313347164042</v>
+        <v>6.232402902258574</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09480059933771193</v>
+        <v>0.09519559933771193</v>
       </c>
       <c r="C32">
-        <v>1833.203196326035</v>
+        <v>1796.894034531242</v>
       </c>
       <c r="D32">
-        <v>2325.113196326035</v>
+        <v>2315.871034531242</v>
       </c>
       <c r="E32">
-        <v>812.0099999999999</v>
+        <v>839.0769999999999</v>
       </c>
       <c r="F32">
-        <v>812.0099999999999</v>
+        <v>839.0769999999999</v>
       </c>
       <c r="G32">
         <v>320.1</v>
@@ -3911,45 +3911,45 @@
         <v>274.8</v>
       </c>
       <c r="M32">
-        <v>44.09214299999999</v>
+        <v>46.4009581</v>
       </c>
       <c r="N32">
-        <v>230.707857</v>
+        <v>228.3990419</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>230.707857</v>
+        <v>228.3990419</v>
       </c>
       <c r="Q32">
-        <v>240.407857</v>
+        <v>238.0990419</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1121579990538742</v>
+        <v>0.1131197091850898</v>
       </c>
       <c r="T32">
-        <v>1.293440913638695</v>
+        <v>1.312186434126212</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.232402902258574</v>
+        <v>5.922291505441997</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09519559933771193</v>
+        <v>0.09529059933771195</v>
       </c>
       <c r="C33">
-        <v>1796.894034531242</v>
+        <v>1767.615186110342</v>
       </c>
       <c r="D33">
-        <v>2315.871034531242</v>
+        <v>2313.659186110342</v>
       </c>
       <c r="E33">
-        <v>839.0769999999999</v>
+        <v>866.144</v>
       </c>
       <c r="F33">
-        <v>839.0769999999999</v>
+        <v>866.144</v>
       </c>
       <c r="G33">
         <v>320.1</v>
@@ -3993,28 +3993,28 @@
         <v>274.8</v>
       </c>
       <c r="M33">
-        <v>46.4009581</v>
+        <v>47.8977632</v>
       </c>
       <c r="N33">
-        <v>228.3990419</v>
+        <v>226.9022368</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>228.3990419</v>
+        <v>226.9022368</v>
       </c>
       <c r="Q33">
-        <v>238.0990419</v>
+        <v>236.6022368</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1131197091850898</v>
+        <v>0.1141097049083999</v>
       </c>
       <c r="T33">
-        <v>1.312186434126212</v>
+        <v>1.331483293451598</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.922291505441997</v>
+        <v>5.737219895896935</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09529059933771195</v>
+        <v>0.09538559933771193</v>
       </c>
       <c r="C34">
-        <v>1767.615186110342</v>
+        <v>1738.340558654511</v>
       </c>
       <c r="D34">
-        <v>2313.659186110342</v>
+        <v>2311.451558654511</v>
       </c>
       <c r="E34">
-        <v>866.144</v>
+        <v>893.211</v>
       </c>
       <c r="F34">
-        <v>866.144</v>
+        <v>893.211</v>
       </c>
       <c r="G34">
         <v>320.1</v>
@@ -4075,28 +4075,28 @@
         <v>274.8</v>
       </c>
       <c r="M34">
-        <v>47.8977632</v>
+        <v>49.3945683</v>
       </c>
       <c r="N34">
-        <v>226.9022368</v>
+        <v>225.4054317</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>226.9022368</v>
+        <v>225.4054317</v>
       </c>
       <c r="Q34">
-        <v>236.6022368</v>
+        <v>235.1054317</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1141097049083999</v>
+        <v>0.1151292527428536</v>
       </c>
       <c r="T34">
-        <v>1.331483293451598</v>
+        <v>1.351356178428488</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.737219895896935</v>
+        <v>5.563364747536421</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09538559933771193</v>
+        <v>0.09548059933771193</v>
       </c>
       <c r="C35">
-        <v>1738.340558654511</v>
+        <v>1709.070140092693</v>
       </c>
       <c r="D35">
-        <v>2311.451558654511</v>
+        <v>2309.248140092694</v>
       </c>
       <c r="E35">
-        <v>893.211</v>
+        <v>920.278</v>
       </c>
       <c r="F35">
-        <v>893.211</v>
+        <v>920.278</v>
       </c>
       <c r="G35">
         <v>320.1</v>
@@ -4157,28 +4157,28 @@
         <v>274.8</v>
       </c>
       <c r="M35">
-        <v>49.3945683</v>
+        <v>50.89137340000001</v>
       </c>
       <c r="N35">
-        <v>225.4054317</v>
+        <v>223.9086266</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>225.4054317</v>
+        <v>223.9086266</v>
       </c>
       <c r="Q35">
-        <v>235.1054317</v>
+        <v>233.6086266</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1151292527428536</v>
+        <v>0.1161796959662302</v>
       </c>
       <c r="T35">
-        <v>1.351356178428488</v>
+        <v>1.37183127204104</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.563364747536421</v>
+        <v>5.399736372608879</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09548059933771193</v>
+        <v>0.09557559933771193</v>
       </c>
       <c r="C36">
-        <v>1709.070140092693</v>
+        <v>1679.803918399818</v>
       </c>
       <c r="D36">
-        <v>2309.248140092694</v>
+        <v>2307.048918399818</v>
       </c>
       <c r="E36">
-        <v>920.278</v>
+        <v>947.345</v>
       </c>
       <c r="F36">
-        <v>920.278</v>
+        <v>947.345</v>
       </c>
       <c r="G36">
         <v>320.1</v>
@@ -4239,28 +4239,28 @@
         <v>274.8</v>
       </c>
       <c r="M36">
-        <v>50.89137340000001</v>
+        <v>52.3881785</v>
       </c>
       <c r="N36">
-        <v>223.9086266</v>
+        <v>222.4118215</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>223.9086266</v>
+        <v>222.4118215</v>
       </c>
       <c r="Q36">
-        <v>233.6086266</v>
+        <v>232.1118215</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1161796959662302</v>
+        <v>0.1172624605195568</v>
       </c>
       <c r="T36">
-        <v>1.37183127204104</v>
+        <v>1.39293636853398</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.399736372608879</v>
+        <v>5.24545819053434</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09557559933771193</v>
+        <v>0.09567059933771191</v>
       </c>
       <c r="C37">
-        <v>1679.803918399818</v>
+        <v>1650.541881596579</v>
       </c>
       <c r="D37">
-        <v>2307.048918399818</v>
+        <v>2304.853881596579</v>
       </c>
       <c r="E37">
-        <v>947.345</v>
+        <v>974.412</v>
       </c>
       <c r="F37">
-        <v>947.345</v>
+        <v>974.412</v>
       </c>
       <c r="G37">
         <v>320.1</v>
@@ -4321,28 +4321,28 @@
         <v>274.8</v>
       </c>
       <c r="M37">
-        <v>52.3881785</v>
+        <v>53.88498360000001</v>
       </c>
       <c r="N37">
-        <v>222.4118215</v>
+        <v>220.9150164</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>222.4118215</v>
+        <v>220.9150164</v>
       </c>
       <c r="Q37">
-        <v>232.1118215</v>
+        <v>230.6150164</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1172624605195568</v>
+        <v>0.1183790614651749</v>
       </c>
       <c r="T37">
-        <v>1.39293636853398</v>
+        <v>1.414700999292323</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.24545819053434</v>
+        <v>5.099751018575052</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09567059933771192</v>
+        <v>0.09576559933771195</v>
       </c>
       <c r="C38">
-        <v>1650.541881596579</v>
+        <v>1621.284017749216</v>
       </c>
       <c r="D38">
-        <v>2304.853881596579</v>
+        <v>2302.663017749216</v>
       </c>
       <c r="E38">
-        <v>974.4119999999999</v>
+        <v>1001.479</v>
       </c>
       <c r="F38">
-        <v>974.4119999999999</v>
+        <v>1001.479</v>
       </c>
       <c r="G38">
         <v>320.1</v>
@@ -4403,28 +4403,28 @@
         <v>274.8</v>
       </c>
       <c r="M38">
-        <v>53.8849836</v>
+        <v>55.3817887</v>
       </c>
       <c r="N38">
-        <v>220.9150164</v>
+        <v>219.4182113</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>220.9150164</v>
+        <v>219.4182113</v>
       </c>
       <c r="Q38">
-        <v>230.6150164</v>
+        <v>229.1182113</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1183790614651749</v>
+        <v>0.1195311100598602</v>
       </c>
       <c r="T38">
-        <v>1.414700999292323</v>
+        <v>1.437156570709661</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.099751018575053</v>
+        <v>4.961919909964916</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09576559933771195</v>
+        <v>0.09586059933771193</v>
       </c>
       <c r="C39">
-        <v>1621.284017749216</v>
+        <v>1592.030314969304</v>
       </c>
       <c r="D39">
-        <v>2302.663017749216</v>
+        <v>2300.476314969304</v>
       </c>
       <c r="E39">
-        <v>1001.479</v>
+        <v>1028.546</v>
       </c>
       <c r="F39">
-        <v>1001.479</v>
+        <v>1028.546</v>
       </c>
       <c r="G39">
         <v>320.1</v>
@@ -4485,28 +4485,28 @@
         <v>274.8</v>
       </c>
       <c r="M39">
-        <v>55.3817887</v>
+        <v>56.8785938</v>
       </c>
       <c r="N39">
-        <v>219.4182113</v>
+        <v>217.9214062</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>219.4182113</v>
+        <v>217.9214062</v>
       </c>
       <c r="Q39">
-        <v>229.1182113</v>
+        <v>227.6214062</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1195311100598602</v>
+        <v>0.1207203215124386</v>
       </c>
       <c r="T39">
-        <v>1.437156570709661</v>
+        <v>1.460336515398527</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.961919909964916</v>
+        <v>4.831343070228996</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09586059933771193</v>
+        <v>0.09595559933771193</v>
       </c>
       <c r="C40">
-        <v>1592.030314969304</v>
+        <v>1562.78076141353</v>
       </c>
       <c r="D40">
-        <v>2300.476314969304</v>
+        <v>2298.29376141353</v>
       </c>
       <c r="E40">
-        <v>1028.546</v>
+        <v>1055.613</v>
       </c>
       <c r="F40">
-        <v>1028.546</v>
+        <v>1055.613</v>
       </c>
       <c r="G40">
         <v>320.1</v>
@@ -4567,28 +4567,28 @@
         <v>274.8</v>
       </c>
       <c r="M40">
-        <v>56.8785938</v>
+        <v>58.37539890000001</v>
       </c>
       <c r="N40">
-        <v>217.9214062</v>
+        <v>216.4246011</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>217.9214062</v>
+        <v>216.4246011</v>
       </c>
       <c r="Q40">
-        <v>227.6214062</v>
+        <v>226.1246011</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1207203215124386</v>
+        <v>0.1219485235044458</v>
       </c>
       <c r="T40">
-        <v>1.460336515398527</v>
+        <v>1.484276458273913</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.831343070228996</v>
+        <v>4.707462478684663</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09595559933771193</v>
+        <v>0.09605059933771193</v>
       </c>
       <c r="C41">
-        <v>1562.78076141353</v>
+        <v>1533.535345283485</v>
       </c>
       <c r="D41">
-        <v>2298.29376141353</v>
+        <v>2296.115345283486</v>
       </c>
       <c r="E41">
-        <v>1055.613</v>
+        <v>1082.68</v>
       </c>
       <c r="F41">
-        <v>1055.613</v>
+        <v>1082.68</v>
       </c>
       <c r="G41">
         <v>320.1</v>
@@ -4649,28 +4649,28 @@
         <v>274.8</v>
       </c>
       <c r="M41">
-        <v>58.37539890000001</v>
+        <v>59.872204</v>
       </c>
       <c r="N41">
-        <v>216.4246011</v>
+        <v>214.927796</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>216.4246011</v>
+        <v>214.927796</v>
       </c>
       <c r="Q41">
-        <v>226.1246011</v>
+        <v>224.627796</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1219485235044458</v>
+        <v>0.1232176655628532</v>
       </c>
       <c r="T41">
-        <v>1.484276458273913</v>
+        <v>1.509014399245144</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.707462478684663</v>
+        <v>4.589775916717548</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09605059933771193</v>
+        <v>0.09717059933771194</v>
       </c>
       <c r="C42">
-        <v>1533.535345283485</v>
+        <v>1481.093856729359</v>
       </c>
       <c r="D42">
-        <v>2296.115345283486</v>
+        <v>2270.740856729359</v>
       </c>
       <c r="E42">
-        <v>1082.68</v>
+        <v>1109.747</v>
       </c>
       <c r="F42">
-        <v>1082.68</v>
+        <v>1109.747</v>
       </c>
       <c r="G42">
         <v>320.1</v>
@@ -4731,45 +4731,45 @@
         <v>274.8</v>
       </c>
       <c r="M42">
-        <v>59.872204</v>
+        <v>64.14337660000001</v>
       </c>
       <c r="N42">
-        <v>214.927796</v>
+        <v>210.6566234</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>214.927796</v>
+        <v>210.6566234</v>
       </c>
       <c r="Q42">
-        <v>224.627796</v>
+        <v>220.3566234</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1232176655628532</v>
+        <v>0.1245298293859524</v>
       </c>
       <c r="T42">
-        <v>1.509014399245144</v>
+        <v>1.534590914486587</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.589775916717548</v>
+        <v>4.284152387450086</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09717059933771194</v>
+        <v>0.09729059933771193</v>
       </c>
       <c r="C43">
-        <v>1481.093856729359</v>
+        <v>1451.341385675785</v>
       </c>
       <c r="D43">
-        <v>2270.740856729359</v>
+        <v>2268.055385675786</v>
       </c>
       <c r="E43">
-        <v>1109.747</v>
+        <v>1136.814</v>
       </c>
       <c r="F43">
-        <v>1109.747</v>
+        <v>1136.814</v>
       </c>
       <c r="G43">
         <v>320.1</v>
@@ -4813,28 +4813,28 @@
         <v>274.8</v>
       </c>
       <c r="M43">
-        <v>64.14337660000001</v>
+        <v>65.70784920000001</v>
       </c>
       <c r="N43">
-        <v>210.6566234</v>
+        <v>209.0921508</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>210.6566234</v>
+        <v>209.0921508</v>
       </c>
       <c r="Q43">
-        <v>220.3566234</v>
+        <v>218.7921508</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1245298293859524</v>
+        <v>0.1258872402374344</v>
       </c>
       <c r="T43">
-        <v>1.534590914486587</v>
+        <v>1.56104937852946</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.284152387450086</v>
+        <v>4.182148759177465</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09729059933771195</v>
+        <v>0.09741059933771193</v>
       </c>
       <c r="C44">
-        <v>1451.341385675786</v>
+        <v>1421.595259014984</v>
       </c>
       <c r="D44">
-        <v>2268.055385675786</v>
+        <v>2265.376259014984</v>
       </c>
       <c r="E44">
-        <v>1136.814</v>
+        <v>1163.881</v>
       </c>
       <c r="F44">
-        <v>1136.814</v>
+        <v>1163.881</v>
       </c>
       <c r="G44">
         <v>320.1</v>
@@ -4895,28 +4895,28 @@
         <v>274.8</v>
       </c>
       <c r="M44">
-        <v>65.7078492</v>
+        <v>67.2723218</v>
       </c>
       <c r="N44">
-        <v>209.0921508</v>
+        <v>207.5276782</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>209.0921508</v>
+        <v>207.5276782</v>
       </c>
       <c r="Q44">
-        <v>218.7921508</v>
+        <v>217.2276782</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1258872402374344</v>
+        <v>0.1272922795398455</v>
       </c>
       <c r="T44">
-        <v>1.56104937852946</v>
+        <v>1.588436209731731</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.182148759177466</v>
+        <v>4.084889485708223</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09741059933771193</v>
+        <v>0.09907059933771192</v>
       </c>
       <c r="C45">
-        <v>1421.595259014984</v>
+        <v>1358.105945561325</v>
       </c>
       <c r="D45">
-        <v>2265.376259014984</v>
+        <v>2228.953945561325</v>
       </c>
       <c r="E45">
-        <v>1163.881</v>
+        <v>1190.948</v>
       </c>
       <c r="F45">
-        <v>1163.881</v>
+        <v>1190.948</v>
       </c>
       <c r="G45">
         <v>320.1</v>
@@ -4977,45 +4977,45 @@
         <v>274.8</v>
       </c>
       <c r="M45">
-        <v>67.2723218</v>
+        <v>73.00511239999999</v>
       </c>
       <c r="N45">
-        <v>207.5276782</v>
+        <v>201.7948876</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>207.5276782</v>
+        <v>201.7948876</v>
       </c>
       <c r="Q45">
-        <v>217.2276782</v>
+        <v>211.4948876</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1272922795398455</v>
+        <v>0.1287474988173427</v>
       </c>
       <c r="T45">
-        <v>1.588436209731731</v>
+        <v>1.616801142048369</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.084889485708223</v>
+        <v>3.764119949495483</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09907059933771192</v>
+        <v>0.09922559933771194</v>
       </c>
       <c r="C46">
-        <v>1358.105945561325</v>
+        <v>1327.697761539884</v>
       </c>
       <c r="D46">
-        <v>2228.953945561325</v>
+        <v>2225.612761539884</v>
       </c>
       <c r="E46">
-        <v>1190.948</v>
+        <v>1218.015</v>
       </c>
       <c r="F46">
-        <v>1190.948</v>
+        <v>1218.015</v>
       </c>
       <c r="G46">
         <v>320.1</v>
@@ -5059,28 +5059,28 @@
         <v>274.8</v>
       </c>
       <c r="M46">
-        <v>73.00511239999999</v>
+        <v>74.66431949999999</v>
       </c>
       <c r="N46">
-        <v>201.7948876</v>
+        <v>200.1356805</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>201.7948876</v>
+        <v>200.1356805</v>
       </c>
       <c r="Q46">
-        <v>211.4948876</v>
+        <v>209.8356805</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1287474988173427</v>
+        <v>0.1302556351594762</v>
       </c>
       <c r="T46">
-        <v>1.616801142048369</v>
+        <v>1.646197526449248</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.764119949495483</v>
+        <v>3.680472839506694</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09922559933771194</v>
+        <v>0.09938059933771194</v>
       </c>
       <c r="C47">
-        <v>1327.697761539884</v>
+        <v>1297.299579341694</v>
       </c>
       <c r="D47">
-        <v>2225.612761539884</v>
+        <v>2222.281579341694</v>
       </c>
       <c r="E47">
-        <v>1218.015</v>
+        <v>1245.082</v>
       </c>
       <c r="F47">
-        <v>1218.015</v>
+        <v>1245.082</v>
       </c>
       <c r="G47">
         <v>320.1</v>
@@ -5141,28 +5141,28 @@
         <v>274.8</v>
       </c>
       <c r="M47">
-        <v>74.66431949999999</v>
+        <v>76.32352659999999</v>
       </c>
       <c r="N47">
-        <v>200.1356805</v>
+        <v>198.4764734</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>200.1356805</v>
+        <v>198.4764734</v>
       </c>
       <c r="Q47">
-        <v>209.8356805</v>
+        <v>208.1764734</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1302556351594762</v>
+        <v>0.1318196284031702</v>
       </c>
       <c r="T47">
-        <v>1.646197526449248</v>
+        <v>1.676682665827938</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.680472839506694</v>
+        <v>3.600462560386984</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09938059933771194</v>
+        <v>0.09953559933771193</v>
       </c>
       <c r="C48">
-        <v>1297.299579341694</v>
+        <v>1266.911354123238</v>
       </c>
       <c r="D48">
-        <v>2222.281579341694</v>
+        <v>2218.960354123238</v>
       </c>
       <c r="E48">
-        <v>1245.082</v>
+        <v>1272.149</v>
       </c>
       <c r="F48">
-        <v>1245.082</v>
+        <v>1272.149</v>
       </c>
       <c r="G48">
         <v>320.1</v>
@@ -5223,28 +5223,28 @@
         <v>274.8</v>
       </c>
       <c r="M48">
-        <v>76.32352659999999</v>
+        <v>77.9827337</v>
       </c>
       <c r="N48">
-        <v>198.4764734</v>
+        <v>196.8172663</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>198.4764734</v>
+        <v>196.8172663</v>
       </c>
       <c r="Q48">
-        <v>208.1764734</v>
+        <v>206.5172663</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1318196284031702</v>
+        <v>0.1334426402598338</v>
       </c>
       <c r="T48">
-        <v>1.676682665827938</v>
+        <v>1.708318187824692</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.600462560386984</v>
+        <v>3.523856973995771</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09953559933771193</v>
+        <v>0.1010345993377119</v>
       </c>
       <c r="C49">
-        <v>1266.911354123238</v>
+        <v>1208.229831524795</v>
       </c>
       <c r="D49">
-        <v>2218.960354123238</v>
+        <v>2187.345831524795</v>
       </c>
       <c r="E49">
-        <v>1272.149</v>
+        <v>1299.216</v>
       </c>
       <c r="F49">
-        <v>1272.149</v>
+        <v>1299.216</v>
       </c>
       <c r="G49">
         <v>320.1</v>
@@ -5305,45 +5305,45 @@
         <v>274.8</v>
       </c>
       <c r="M49">
-        <v>77.9827337</v>
+        <v>83.27974560000001</v>
       </c>
       <c r="N49">
-        <v>196.8172663</v>
+        <v>191.5202544</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>196.8172663</v>
+        <v>191.5202544</v>
       </c>
       <c r="Q49">
-        <v>206.5172663</v>
+        <v>201.2202544</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1334426402598338</v>
+        <v>0.135128075649446</v>
       </c>
       <c r="T49">
-        <v>1.708318187824692</v>
+        <v>1.741170460667474</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.523856973995771</v>
+        <v>3.299721895404061</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1010345993377119</v>
+        <v>0.1012175993377119</v>
       </c>
       <c r="C50">
-        <v>1208.229831524795</v>
+        <v>1177.364881360107</v>
       </c>
       <c r="D50">
-        <v>2187.345831524795</v>
+        <v>2183.547881360107</v>
       </c>
       <c r="E50">
-        <v>1299.216</v>
+        <v>1326.283</v>
       </c>
       <c r="F50">
-        <v>1299.216</v>
+        <v>1326.283</v>
       </c>
       <c r="G50">
         <v>320.1</v>
@@ -5387,28 +5387,28 @@
         <v>274.8</v>
       </c>
       <c r="M50">
-        <v>83.2797456</v>
+        <v>85.0147403</v>
       </c>
       <c r="N50">
-        <v>191.5202544</v>
+        <v>189.7852597</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>191.5202544</v>
+        <v>189.7852597</v>
       </c>
       <c r="Q50">
-        <v>201.2202544</v>
+        <v>199.4852597</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.135128075649446</v>
+        <v>0.1368796065445332</v>
       </c>
       <c r="T50">
-        <v>1.741170460667474</v>
+        <v>1.775311057935464</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.299721895404061</v>
+        <v>3.232380632232549</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1012175993377119</v>
+        <v>0.1014005993377119</v>
       </c>
       <c r="C51">
-        <v>1177.364881360107</v>
+        <v>1146.513097310371</v>
       </c>
       <c r="D51">
-        <v>2183.547881360107</v>
+        <v>2179.763097310371</v>
       </c>
       <c r="E51">
-        <v>1326.283</v>
+        <v>1353.35</v>
       </c>
       <c r="F51">
-        <v>1326.283</v>
+        <v>1353.35</v>
       </c>
       <c r="G51">
         <v>320.1</v>
@@ -5469,28 +5469,28 @@
         <v>274.8</v>
       </c>
       <c r="M51">
-        <v>85.0147403</v>
+        <v>86.749735</v>
       </c>
       <c r="N51">
-        <v>189.7852597</v>
+        <v>188.050265</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>189.7852597</v>
+        <v>188.050265</v>
       </c>
       <c r="Q51">
-        <v>199.4852597</v>
+        <v>197.750265</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1368796065445332</v>
+        <v>0.1387011986754239</v>
       </c>
       <c r="T51">
-        <v>1.775311057935464</v>
+        <v>1.810817279094173</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.232380632232549</v>
+        <v>3.167733019587899</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1014005993377119</v>
+        <v>0.1015835993377119</v>
       </c>
       <c r="C52">
-        <v>1146.513097310371</v>
+        <v>1115.674411030835</v>
       </c>
       <c r="D52">
-        <v>2179.763097310371</v>
+        <v>2175.991411030835</v>
       </c>
       <c r="E52">
-        <v>1353.35</v>
+        <v>1380.417</v>
       </c>
       <c r="F52">
-        <v>1353.35</v>
+        <v>1380.417</v>
       </c>
       <c r="G52">
         <v>320.1</v>
@@ -5551,28 +5551,28 @@
         <v>274.8</v>
       </c>
       <c r="M52">
-        <v>86.749735</v>
+        <v>88.4847297</v>
       </c>
       <c r="N52">
-        <v>188.050265</v>
+        <v>186.3152703</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>188.050265</v>
+        <v>186.3152703</v>
       </c>
       <c r="Q52">
-        <v>197.750265</v>
+        <v>196.0152703</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1387011986754239</v>
+        <v>0.1405971415055346</v>
       </c>
       <c r="T52">
-        <v>1.810817279094173</v>
+        <v>1.847772733769565</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.167733019587899</v>
+        <v>3.105620607439116</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1015835993377119</v>
+        <v>0.1017665993377119</v>
       </c>
       <c r="C53">
-        <v>1115.674411030835</v>
+        <v>1084.848754648968</v>
       </c>
       <c r="D53">
-        <v>2175.991411030835</v>
+        <v>2172.232754648968</v>
       </c>
       <c r="E53">
-        <v>1380.417</v>
+        <v>1407.484</v>
       </c>
       <c r="F53">
-        <v>1380.417</v>
+        <v>1407.484</v>
       </c>
       <c r="G53">
         <v>320.1</v>
@@ -5633,28 +5633,28 @@
         <v>274.8</v>
       </c>
       <c r="M53">
-        <v>88.4847297</v>
+        <v>90.2197244</v>
       </c>
       <c r="N53">
-        <v>186.3152703</v>
+        <v>184.5802756</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>186.3152703</v>
+        <v>184.5802756</v>
       </c>
       <c r="Q53">
-        <v>196.0152703</v>
+        <v>194.2802756</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1405971415055346</v>
+        <v>0.1425720819535665</v>
       </c>
       <c r="T53">
-        <v>1.847772733769565</v>
+        <v>1.886267999056431</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.105620607439116</v>
+        <v>3.045897134219133</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1017665993377119</v>
+        <v>0.1060835993377119</v>
       </c>
       <c r="C54">
-        <v>1084.848754648968</v>
+        <v>972.733153465053</v>
       </c>
       <c r="D54">
-        <v>2172.232754648968</v>
+        <v>2087.184153465053</v>
       </c>
       <c r="E54">
-        <v>1407.484</v>
+        <v>1434.551</v>
       </c>
       <c r="F54">
-        <v>1407.484</v>
+        <v>1434.551</v>
       </c>
       <c r="G54">
         <v>320.1</v>
@@ -5715,45 +5715,45 @@
         <v>274.8</v>
       </c>
       <c r="M54">
-        <v>90.2197244</v>
+        <v>103.1442169</v>
       </c>
       <c r="N54">
-        <v>184.5802756</v>
+        <v>171.6557831</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>184.5802756</v>
+        <v>171.6557831</v>
       </c>
       <c r="Q54">
-        <v>194.2802756</v>
+        <v>181.3557831</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1425720819535665</v>
+        <v>0.1446310624206637</v>
       </c>
       <c r="T54">
-        <v>1.886267999056431</v>
+        <v>1.926401360738482</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.045897134219133</v>
+        <v>2.664230804781067</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1060835993377119</v>
+        <v>0.1063445993377119</v>
       </c>
       <c r="C55">
-        <v>972.733153465053</v>
+        <v>940.7372168357701</v>
       </c>
       <c r="D55">
-        <v>2087.184153465053</v>
+        <v>2082.25521683577</v>
       </c>
       <c r="E55">
-        <v>1434.551</v>
+        <v>1461.618</v>
       </c>
       <c r="F55">
-        <v>1434.551</v>
+        <v>1461.618</v>
       </c>
       <c r="G55">
         <v>320.1</v>
@@ -5797,28 +5797,28 @@
         <v>274.8</v>
       </c>
       <c r="M55">
-        <v>103.1442169</v>
+        <v>105.0903342</v>
       </c>
       <c r="N55">
-        <v>171.6557831</v>
+        <v>169.7096658</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>171.6557831</v>
+        <v>169.7096658</v>
       </c>
       <c r="Q55">
-        <v>181.3557831</v>
+        <v>179.4096658</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1446310624206637</v>
+        <v>0.1467795637776346</v>
       </c>
       <c r="T55">
-        <v>1.926401360738482</v>
+        <v>1.968279651189319</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.664230804781067</v>
+        <v>2.614893197285122</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1063445993377119</v>
+        <v>0.1066055993377119</v>
       </c>
       <c r="C56">
-        <v>940.7372168357701</v>
+        <v>908.764504970397</v>
       </c>
       <c r="D56">
-        <v>2082.25521683577</v>
+        <v>2077.349504970397</v>
       </c>
       <c r="E56">
-        <v>1461.618</v>
+        <v>1488.685</v>
       </c>
       <c r="F56">
-        <v>1461.618</v>
+        <v>1488.685</v>
       </c>
       <c r="G56">
         <v>320.1</v>
@@ -5879,28 +5879,28 @@
         <v>274.8</v>
       </c>
       <c r="M56">
-        <v>105.0903342</v>
+        <v>107.0364515</v>
       </c>
       <c r="N56">
-        <v>169.7096658</v>
+        <v>167.7635485</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>169.7096658</v>
+        <v>167.7635485</v>
       </c>
       <c r="Q56">
-        <v>179.4096658</v>
+        <v>177.4635485</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1467795637776346</v>
+        <v>0.1490235540838043</v>
       </c>
       <c r="T56">
-        <v>1.968279651189319</v>
+        <v>2.012019198993526</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.614893197285122</v>
+        <v>2.567349684607211</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1066055993377119</v>
+        <v>0.1068665993377119</v>
       </c>
       <c r="C57">
-        <v>908.764504970397</v>
+        <v>876.8148541048495</v>
       </c>
       <c r="D57">
-        <v>2077.349504970397</v>
+        <v>2072.46685410485</v>
       </c>
       <c r="E57">
-        <v>1488.685</v>
+        <v>1515.752</v>
       </c>
       <c r="F57">
-        <v>1488.685</v>
+        <v>1515.752</v>
       </c>
       <c r="G57">
         <v>320.1</v>
@@ -5961,28 +5961,28 @@
         <v>274.8</v>
       </c>
       <c r="M57">
-        <v>107.0364515</v>
+        <v>108.9825688</v>
       </c>
       <c r="N57">
-        <v>167.7635485</v>
+        <v>165.8174312</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>167.7635485</v>
+        <v>165.8174312</v>
       </c>
       <c r="Q57">
-        <v>177.4635485</v>
+        <v>175.5174312</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1490235540838043</v>
+        <v>0.1513695439493453</v>
       </c>
       <c r="T57">
-        <v>2.012019198993526</v>
+        <v>2.05774690806156</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.567349684607211</v>
+        <v>2.521504154524939</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1068665993377119</v>
+        <v>0.1093505993377119</v>
       </c>
       <c r="C58">
-        <v>876.8148541048495</v>
+        <v>804.4020744705576</v>
       </c>
       <c r="D58">
-        <v>2072.46685410485</v>
+        <v>2027.121074470558</v>
       </c>
       <c r="E58">
-        <v>1515.752</v>
+        <v>1542.819</v>
       </c>
       <c r="F58">
-        <v>1515.752</v>
+        <v>1542.819</v>
       </c>
       <c r="G58">
         <v>320.1</v>
@@ -6043,45 +6043,45 @@
         <v>274.8</v>
       </c>
       <c r="M58">
-        <v>108.9825688</v>
+        <v>116.9456802</v>
       </c>
       <c r="N58">
-        <v>165.8174312</v>
+        <v>157.8543198</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>165.8174312</v>
+        <v>157.8543198</v>
       </c>
       <c r="Q58">
-        <v>175.5174312</v>
+        <v>167.5543198</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1513695439493453</v>
+        <v>0.1538246496225859</v>
       </c>
       <c r="T58">
-        <v>2.05774690806156</v>
+        <v>2.105601487318807</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0</v>
       </c>
       <c r="W58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.521504154524939</v>
+        <v>2.34980889871296</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1093505993377119</v>
+        <v>0.1096505993377119</v>
       </c>
       <c r="C59">
-        <v>804.4020744705576</v>
+        <v>771.9924762921603</v>
       </c>
       <c r="D59">
-        <v>2027.121074470558</v>
+        <v>2021.778476292161</v>
       </c>
       <c r="E59">
-        <v>1542.819</v>
+        <v>1569.886</v>
       </c>
       <c r="F59">
-        <v>1542.819</v>
+        <v>1569.886</v>
       </c>
       <c r="G59">
         <v>320.1</v>
@@ -6125,28 +6125,28 @@
         <v>274.8</v>
       </c>
       <c r="M59">
-        <v>116.9456802</v>
+        <v>118.9973588</v>
       </c>
       <c r="N59">
-        <v>157.8543198</v>
+        <v>155.8026412</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>157.8543198</v>
+        <v>155.8026412</v>
       </c>
       <c r="Q59">
-        <v>167.5543198</v>
+        <v>165.5026412</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1538246496225859</v>
+        <v>0.1563966650897903</v>
       </c>
       <c r="T59">
-        <v>2.105601487318807</v>
+        <v>2.155734856064492</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.34980889871296</v>
+        <v>2.309294952183426</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1096505993377119</v>
+        <v>0.1099505993377119</v>
       </c>
       <c r="C60">
-        <v>771.9924762921607</v>
+        <v>739.6109655582579</v>
       </c>
       <c r="D60">
-        <v>2021.778476292161</v>
+        <v>2016.463965558258</v>
       </c>
       <c r="E60">
-        <v>1569.886</v>
+        <v>1596.953</v>
       </c>
       <c r="F60">
-        <v>1569.886</v>
+        <v>1596.953</v>
       </c>
       <c r="G60">
         <v>320.1</v>
@@ -6207,28 +6207,28 @@
         <v>274.8</v>
       </c>
       <c r="M60">
-        <v>118.9973588</v>
+        <v>121.0490374</v>
       </c>
       <c r="N60">
-        <v>155.8026412</v>
+        <v>153.7509626</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>155.8026412</v>
+        <v>153.7509626</v>
       </c>
       <c r="Q60">
-        <v>165.5026412</v>
+        <v>163.4509626</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1563966650897903</v>
+        <v>0.1590941447261266</v>
       </c>
       <c r="T60">
-        <v>2.155734856064492</v>
+        <v>2.208313754992894</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.309294952183427</v>
+        <v>2.270154359773538</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1099505993377119</v>
+        <v>0.1102505993377119</v>
       </c>
       <c r="C61">
-        <v>739.6109655582579</v>
+        <v>707.2573213549197</v>
       </c>
       <c r="D61">
-        <v>2016.463965558258</v>
+        <v>2011.17732135492</v>
       </c>
       <c r="E61">
-        <v>1596.953</v>
+        <v>1624.02</v>
       </c>
       <c r="F61">
-        <v>1596.953</v>
+        <v>1624.02</v>
       </c>
       <c r="G61">
         <v>320.1</v>
@@ -6289,28 +6289,28 @@
         <v>274.8</v>
       </c>
       <c r="M61">
-        <v>121.0490374</v>
+        <v>123.100716</v>
       </c>
       <c r="N61">
-        <v>153.7509626</v>
+        <v>151.699284</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>153.7509626</v>
+        <v>151.699284</v>
       </c>
       <c r="Q61">
-        <v>163.4509626</v>
+        <v>161.399284</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1590941447261266</v>
+        <v>0.1619264983442798</v>
       </c>
       <c r="T61">
-        <v>2.208313754992894</v>
+        <v>2.263521598867717</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.270154359773538</v>
+        <v>2.232318453777312</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1102505993377119</v>
+        <v>0.1105505993377119</v>
       </c>
       <c r="C62">
-        <v>707.2573213549197</v>
+        <v>674.9313250788762</v>
       </c>
       <c r="D62">
-        <v>2011.17732135492</v>
+        <v>2005.918325078876</v>
       </c>
       <c r="E62">
-        <v>1624.02</v>
+        <v>1651.087</v>
       </c>
       <c r="F62">
-        <v>1624.02</v>
+        <v>1651.087</v>
       </c>
       <c r="G62">
         <v>320.1</v>
@@ -6371,28 +6371,28 @@
         <v>274.8</v>
       </c>
       <c r="M62">
-        <v>123.100716</v>
+        <v>125.1523946</v>
       </c>
       <c r="N62">
-        <v>151.699284</v>
+        <v>149.6476054</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>151.699284</v>
+        <v>149.6476054</v>
       </c>
       <c r="Q62">
-        <v>161.399284</v>
+        <v>159.3476054</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1619264983442798</v>
+        <v>0.164904100865928</v>
       </c>
       <c r="T62">
-        <v>2.263521598867717</v>
+        <v>2.321560614223299</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.232318453777312</v>
+        <v>2.195723069289159</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1105505993377119</v>
+        <v>0.1108505993377119</v>
       </c>
       <c r="C63">
-        <v>674.9313250788762</v>
+        <v>642.6327604073811</v>
       </c>
       <c r="D63">
-        <v>2005.918325078876</v>
+        <v>2000.686760407381</v>
       </c>
       <c r="E63">
-        <v>1651.087</v>
+        <v>1678.154</v>
       </c>
       <c r="F63">
-        <v>1651.087</v>
+        <v>1678.154</v>
       </c>
       <c r="G63">
         <v>320.1</v>
@@ -6453,28 +6453,28 @@
         <v>274.8</v>
       </c>
       <c r="M63">
-        <v>125.1523946</v>
+        <v>127.2040732</v>
       </c>
       <c r="N63">
-        <v>149.6476054</v>
+        <v>147.5959268</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>149.6476054</v>
+        <v>147.5959268</v>
       </c>
       <c r="Q63">
-        <v>159.3476054</v>
+        <v>157.2959268</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.164904100865928</v>
+        <v>0.1680384193097682</v>
       </c>
       <c r="T63">
-        <v>2.321560614223299</v>
+        <v>2.382654314597596</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.195723069289159</v>
+        <v>2.160308181074818</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1108505993377119</v>
+        <v>0.1111505993377119</v>
       </c>
       <c r="C64">
-        <v>642.6327604073811</v>
+        <v>610.3614132685539</v>
       </c>
       <c r="D64">
-        <v>2000.686760407381</v>
+        <v>1995.482413268554</v>
       </c>
       <c r="E64">
-        <v>1678.154</v>
+        <v>1705.221</v>
       </c>
       <c r="F64">
-        <v>1678.154</v>
+        <v>1705.221</v>
       </c>
       <c r="G64">
         <v>320.1</v>
@@ -6535,28 +6535,28 @@
         <v>274.8</v>
       </c>
       <c r="M64">
-        <v>127.2040732</v>
+        <v>129.2557518</v>
       </c>
       <c r="N64">
-        <v>147.5959268</v>
+        <v>145.5442482</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>147.5959268</v>
+        <v>145.5442482</v>
       </c>
       <c r="Q64">
-        <v>157.2959268</v>
+        <v>155.2442482</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1680384193097682</v>
+        <v>0.1713421603721944</v>
       </c>
       <c r="T64">
-        <v>2.382654314597596</v>
+        <v>2.447050377154288</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.160308181074818</v>
+        <v>2.126017575026011</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1111505993377119</v>
+        <v>0.1114505993377119</v>
       </c>
       <c r="C65">
-        <v>610.3614132685539</v>
+        <v>578.117071812178</v>
       </c>
       <c r="D65">
-        <v>1995.482413268554</v>
+        <v>1990.305071812178</v>
       </c>
       <c r="E65">
-        <v>1705.221</v>
+        <v>1732.288</v>
       </c>
       <c r="F65">
-        <v>1705.221</v>
+        <v>1732.288</v>
       </c>
       <c r="G65">
         <v>320.1</v>
@@ -6617,28 +6617,28 @@
         <v>274.8</v>
       </c>
       <c r="M65">
-        <v>129.2557518</v>
+        <v>131.3074304</v>
       </c>
       <c r="N65">
-        <v>145.5442482</v>
+        <v>143.4925696</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>145.5442482</v>
+        <v>143.4925696</v>
       </c>
       <c r="Q65">
-        <v>155.2442482</v>
+        <v>153.1925696</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1713421603721944</v>
+        <v>0.1748294426047554</v>
       </c>
       <c r="T65">
-        <v>2.447050377154288</v>
+        <v>2.515023998741907</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.126017575026011</v>
+        <v>2.09279855041623</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1114505993377119</v>
+        <v>0.1117505993377119</v>
       </c>
       <c r="C66">
-        <v>578.117071812178</v>
+        <v>545.8995263809556</v>
       </c>
       <c r="D66">
-        <v>1990.305071812178</v>
+        <v>1985.154526380956</v>
       </c>
       <c r="E66">
-        <v>1732.288</v>
+        <v>1759.355</v>
       </c>
       <c r="F66">
-        <v>1732.288</v>
+        <v>1759.355</v>
       </c>
       <c r="G66">
         <v>320.1</v>
@@ -6699,28 +6699,28 @@
         <v>274.8</v>
       </c>
       <c r="M66">
-        <v>131.3074304</v>
+        <v>133.359109</v>
       </c>
       <c r="N66">
-        <v>143.4925696</v>
+        <v>141.440891</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>143.4925696</v>
+        <v>141.440891</v>
       </c>
       <c r="Q66">
-        <v>153.1925696</v>
+        <v>151.140891</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1748294426047554</v>
+        <v>0.1785159981077484</v>
       </c>
       <c r="T66">
-        <v>2.515023998741907</v>
+        <v>2.586881827277391</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.09279855041623</v>
+        <v>2.060601649640596</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1117505993377119</v>
+        <v>0.1120505993377119</v>
       </c>
       <c r="C67">
-        <v>545.8995263809556</v>
+        <v>513.7085694822072</v>
       </c>
       <c r="D67">
-        <v>1985.154526380956</v>
+        <v>1980.030569482207</v>
       </c>
       <c r="E67">
-        <v>1759.355</v>
+        <v>1786.422</v>
       </c>
       <c r="F67">
-        <v>1759.355</v>
+        <v>1786.422</v>
       </c>
       <c r="G67">
         <v>320.1</v>
@@ -6781,28 +6781,28 @@
         <v>274.8</v>
       </c>
       <c r="M67">
-        <v>133.359109</v>
+        <v>135.4107876</v>
       </c>
       <c r="N67">
-        <v>141.440891</v>
+        <v>139.3892124</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>141.440891</v>
+        <v>139.3892124</v>
       </c>
       <c r="Q67">
-        <v>151.140891</v>
+        <v>149.0892124</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1785159981077484</v>
+        <v>0.1824194098167998</v>
       </c>
       <c r="T67">
-        <v>2.586881827277391</v>
+        <v>2.662966586903196</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.060601649640596</v>
+        <v>2.029380412524829</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1120505993377119</v>
+        <v>0.1218645993377119</v>
       </c>
       <c r="C68">
-        <v>513.7085694822072</v>
+        <v>332.4703628671073</v>
       </c>
       <c r="D68">
-        <v>1980.030569482207</v>
+        <v>1825.859362867107</v>
       </c>
       <c r="E68">
-        <v>1786.422</v>
+        <v>1813.489</v>
       </c>
       <c r="F68">
-        <v>1786.422</v>
+        <v>1813.489</v>
       </c>
       <c r="G68">
         <v>320.1</v>
@@ -6863,45 +6863,45 @@
         <v>274.8</v>
       </c>
       <c r="M68">
-        <v>135.4107876</v>
+        <v>163.21401</v>
       </c>
       <c r="N68">
-        <v>139.3892124</v>
+        <v>111.58599</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>139.3892124</v>
+        <v>111.58599</v>
       </c>
       <c r="Q68">
-        <v>149.0892124</v>
+        <v>121.28599</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1824194098167998</v>
+        <v>0.1865593919324604</v>
       </c>
       <c r="T68">
-        <v>2.662966586903196</v>
+        <v>2.743662544082081</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0</v>
       </c>
       <c r="W68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.029380412524829</v>
+        <v>1.683678992998211</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1218645993377119</v>
+        <v>0.1223065993377119</v>
       </c>
       <c r="C69">
-        <v>332.4703628671073</v>
+        <v>299.0228644268823</v>
       </c>
       <c r="D69">
-        <v>1825.859362867107</v>
+        <v>1819.478864426882</v>
       </c>
       <c r="E69">
-        <v>1813.489</v>
+        <v>1840.556</v>
       </c>
       <c r="F69">
-        <v>1813.489</v>
+        <v>1840.556</v>
       </c>
       <c r="G69">
         <v>320.1</v>
@@ -6945,28 +6945,28 @@
         <v>274.8</v>
       </c>
       <c r="M69">
-        <v>163.21401</v>
+        <v>165.65004</v>
       </c>
       <c r="N69">
-        <v>111.58599</v>
+        <v>109.14996</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>111.58599</v>
+        <v>109.14996</v>
       </c>
       <c r="Q69">
-        <v>121.28599</v>
+        <v>118.84996</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1865593919324604</v>
+        <v>0.1909581229303498</v>
       </c>
       <c r="T69">
-        <v>2.743662544082081</v>
+        <v>2.829401998584646</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.683678992998211</v>
+        <v>1.658919007807061</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1223065993377119</v>
+        <v>0.1227485993377119</v>
       </c>
       <c r="C70">
-        <v>299.0228644268823</v>
+        <v>265.6198042299302</v>
       </c>
       <c r="D70">
-        <v>1819.478864426882</v>
+        <v>1813.14280422993</v>
       </c>
       <c r="E70">
-        <v>1840.556</v>
+        <v>1867.623</v>
       </c>
       <c r="F70">
-        <v>1840.556</v>
+        <v>1867.623</v>
       </c>
       <c r="G70">
         <v>320.1</v>
@@ -7027,28 +7027,28 @@
         <v>274.8</v>
       </c>
       <c r="M70">
-        <v>165.65004</v>
+        <v>168.08607</v>
       </c>
       <c r="N70">
-        <v>109.14996</v>
+        <v>106.71393</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>109.14996</v>
+        <v>106.71393</v>
       </c>
       <c r="Q70">
-        <v>118.84996</v>
+        <v>116.41393</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1909581229303498</v>
+        <v>0.1956406430248772</v>
       </c>
       <c r="T70">
-        <v>2.829401998584646</v>
+        <v>2.920673030797054</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.658919007807061</v>
+        <v>1.634876703346089</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1227485993377119</v>
+        <v>0.1231905993377119</v>
       </c>
       <c r="C71">
-        <v>265.6198042299302</v>
+        <v>232.2607196389154</v>
       </c>
       <c r="D71">
-        <v>1813.14280422993</v>
+        <v>1806.850719638915</v>
       </c>
       <c r="E71">
-        <v>1867.623</v>
+        <v>1894.69</v>
       </c>
       <c r="F71">
-        <v>1867.623</v>
+        <v>1894.69</v>
       </c>
       <c r="G71">
         <v>320.1</v>
@@ -7109,28 +7109,28 @@
         <v>274.8</v>
       </c>
       <c r="M71">
-        <v>168.08607</v>
+        <v>170.5221</v>
       </c>
       <c r="N71">
-        <v>106.71393</v>
+        <v>104.2779</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>106.71393</v>
+        <v>104.2779</v>
       </c>
       <c r="Q71">
-        <v>116.41393</v>
+        <v>113.9779</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1956406430248772</v>
+        <v>0.2006353311257065</v>
       </c>
       <c r="T71">
-        <v>2.920673030797054</v>
+        <v>3.018028798490289</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.634876703346089</v>
+        <v>1.611521321869717</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1231905993377119</v>
+        <v>0.1236325993377119</v>
       </c>
       <c r="C72">
-        <v>232.2607196389154</v>
+        <v>198.9451544161871</v>
       </c>
       <c r="D72">
-        <v>1806.850719638915</v>
+        <v>1800.602154416187</v>
       </c>
       <c r="E72">
-        <v>1894.69</v>
+        <v>1921.757</v>
       </c>
       <c r="F72">
-        <v>1894.69</v>
+        <v>1921.757</v>
       </c>
       <c r="G72">
         <v>320.1</v>
@@ -7191,28 +7191,28 @@
         <v>274.8</v>
       </c>
       <c r="M72">
-        <v>170.5221</v>
+        <v>172.95813</v>
       </c>
       <c r="N72">
-        <v>104.2779</v>
+        <v>101.84187</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>104.2779</v>
+        <v>101.84187</v>
       </c>
       <c r="Q72">
-        <v>113.9779</v>
+        <v>111.54187</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2006353311257065</v>
+        <v>0.2059744804748688</v>
       </c>
       <c r="T72">
-        <v>3.018028798490289</v>
+        <v>3.12209875705892</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.611521321869717</v>
+        <v>1.588823838463101</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.123632599337712</v>
+        <v>0.1240745993377119</v>
       </c>
       <c r="C73">
-        <v>198.9451544161868</v>
+        <v>165.6726586135057</v>
       </c>
       <c r="D73">
-        <v>1800.602154416187</v>
+        <v>1794.396658613505</v>
       </c>
       <c r="E73">
-        <v>1921.757</v>
+        <v>1948.824</v>
       </c>
       <c r="F73">
-        <v>1921.757</v>
+        <v>1948.824</v>
       </c>
       <c r="G73">
         <v>320.1</v>
@@ -7273,28 +7273,28 @@
         <v>274.8</v>
       </c>
       <c r="M73">
-        <v>172.95813</v>
+        <v>175.39416</v>
       </c>
       <c r="N73">
-        <v>101.84187</v>
+        <v>99.40584000000004</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
       <c r="P73">
-        <v>101.84187</v>
+        <v>99.40584000000004</v>
       </c>
       <c r="Q73">
-        <v>111.54187</v>
+        <v>109.10584</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2059744804748687</v>
+        <v>0.2116949976346854</v>
       </c>
       <c r="T73">
-        <v>3.122098757058919</v>
+        <v>3.233602284096738</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.588823838463101</v>
+        <v>1.566756840706669</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1240745993377119</v>
+        <v>0.1245165993377119</v>
       </c>
       <c r="C74">
-        <v>165.6726586135057</v>
+        <v>132.4427884640329</v>
       </c>
       <c r="D74">
-        <v>1794.396658613505</v>
+        <v>1788.233788464033</v>
       </c>
       <c r="E74">
-        <v>1948.824</v>
+        <v>1975.891</v>
       </c>
       <c r="F74">
-        <v>1948.824</v>
+        <v>1975.891</v>
       </c>
       <c r="G74">
         <v>320.1</v>
@@ -7355,28 +7355,28 @@
         <v>274.8</v>
       </c>
       <c r="M74">
-        <v>175.39416</v>
+        <v>177.83019</v>
       </c>
       <c r="N74">
-        <v>99.40584000000004</v>
+        <v>96.96981000000002</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>99.40584000000004</v>
+        <v>96.96981000000002</v>
       </c>
       <c r="Q74">
-        <v>109.10584</v>
+        <v>106.66981</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2116949976346854</v>
+        <v>0.2178392568063404</v>
       </c>
       <c r="T74">
-        <v>3.233602284096738</v>
+        <v>3.353365331655876</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.566756840706669</v>
+        <v>1.545294418231235</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1245165993377119</v>
+        <v>0.1249585993377119</v>
       </c>
       <c r="C75">
-        <v>132.4427884640329</v>
+        <v>99.2551062765499</v>
       </c>
       <c r="D75">
-        <v>1788.233788464033</v>
+        <v>1782.11310627655</v>
       </c>
       <c r="E75">
-        <v>1975.891</v>
+        <v>2002.958</v>
       </c>
       <c r="F75">
-        <v>1975.891</v>
+        <v>2002.958</v>
       </c>
       <c r="G75">
         <v>320.1</v>
@@ -7437,28 +7437,28 @@
         <v>274.8</v>
       </c>
       <c r="M75">
-        <v>177.83019</v>
+        <v>180.26622</v>
       </c>
       <c r="N75">
-        <v>96.96981000000002</v>
+        <v>94.53378000000004</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>96.96981000000002</v>
+        <v>94.53378000000004</v>
       </c>
       <c r="Q75">
-        <v>106.66981</v>
+        <v>104.23378</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2178392568063404</v>
+        <v>0.224456151298892</v>
       </c>
       <c r="T75">
-        <v>3.353365331655876</v>
+        <v>3.482340921334948</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.545294418231235</v>
+        <v>1.52441206122811</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1249585993377119</v>
+        <v>0.1254005993377119</v>
       </c>
       <c r="C76">
-        <v>99.2551062765499</v>
+        <v>66.10918033182975</v>
       </c>
       <c r="D76">
-        <v>1782.11310627655</v>
+        <v>1776.034180331829</v>
       </c>
       <c r="E76">
-        <v>2002.958</v>
+        <v>2030.025</v>
       </c>
       <c r="F76">
-        <v>2002.958</v>
+        <v>2030.025</v>
       </c>
       <c r="G76">
         <v>320.1</v>
@@ -7519,28 +7519,28 @@
         <v>274.8</v>
       </c>
       <c r="M76">
-        <v>180.26622</v>
+        <v>182.70225</v>
       </c>
       <c r="N76">
-        <v>94.53378000000004</v>
+        <v>92.09775000000002</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>94.53378000000004</v>
+        <v>92.09775000000002</v>
       </c>
       <c r="Q76">
-        <v>104.23378</v>
+        <v>101.79775</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.224456151298892</v>
+        <v>0.2316023973508477</v>
       </c>
       <c r="T76">
-        <v>3.482340921334948</v>
+        <v>3.621634558188346</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.52441206122811</v>
+        <v>1.504086567078402</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1254005993377119</v>
+        <v>0.169010599337712</v>
       </c>
       <c r="C77">
-        <v>66.10918033182975</v>
+        <v>-408.1766197592765</v>
       </c>
       <c r="D77">
-        <v>1776.034180331829</v>
+        <v>1328.815380240724</v>
       </c>
       <c r="E77">
-        <v>2030.025</v>
+        <v>2057.092</v>
       </c>
       <c r="F77">
-        <v>2030.025</v>
+        <v>2057.092</v>
       </c>
       <c r="G77">
         <v>320.1</v>
@@ -7601,45 +7601,45 @@
         <v>274.8</v>
       </c>
       <c r="M77">
-        <v>182.70225</v>
+        <v>301.9811056</v>
       </c>
       <c r="N77">
-        <v>92.09775000000002</v>
+        <v>-27.18110560000002</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P77">
-        <v>92.09775000000002</v>
+        <v>-27.18110560000002</v>
       </c>
       <c r="Q77">
-        <v>101.79775</v>
+        <v>-17.48110560000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2316023973508477</v>
+        <v>0.2393441639071331</v>
       </c>
       <c r="T77">
-        <v>3.621634558188346</v>
+        <v>3.772535998112861</v>
       </c>
       <c r="U77">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V77">
         <v>0</v>
       </c>
       <c r="W77">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.504086567078402</v>
+        <v>0.9099907077100257</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.169010599337712</v>
+        <v>0.1700205993377119</v>
       </c>
       <c r="C78">
-        <v>-408.1766197592765</v>
+        <v>-442.9480991108576</v>
       </c>
       <c r="D78">
-        <v>1328.815380240724</v>
+        <v>1321.110900889142</v>
       </c>
       <c r="E78">
-        <v>2057.092</v>
+        <v>2084.159</v>
       </c>
       <c r="F78">
-        <v>2057.092</v>
+        <v>2084.159</v>
       </c>
       <c r="G78">
         <v>320.1</v>
@@ -7683,28 +7683,28 @@
         <v>274.8</v>
       </c>
       <c r="M78">
-        <v>301.9811056</v>
+        <v>305.9545412000001</v>
       </c>
       <c r="N78">
-        <v>-27.18110560000002</v>
+        <v>-31.15454120000004</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-27.18110560000002</v>
+        <v>-31.15454120000004</v>
       </c>
       <c r="Q78">
-        <v>-17.48110560000003</v>
+        <v>-21.45454120000005</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2393441639071331</v>
+        <v>0.2477591275552692</v>
       </c>
       <c r="T78">
-        <v>3.772535998112861</v>
+        <v>3.936559302378637</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9099907077100257</v>
+        <v>0.8981726465709343</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1700205993377119</v>
+        <v>0.1710305993377119</v>
       </c>
       <c r="C79">
-        <v>-442.9480991108576</v>
+        <v>-477.6307522446277</v>
       </c>
       <c r="D79">
-        <v>1321.110900889142</v>
+        <v>1313.495247755372</v>
       </c>
       <c r="E79">
-        <v>2084.159</v>
+        <v>2111.226</v>
       </c>
       <c r="F79">
-        <v>2084.159</v>
+        <v>2111.226</v>
       </c>
       <c r="G79">
         <v>320.1</v>
@@ -7765,28 +7765,28 @@
         <v>274.8</v>
       </c>
       <c r="M79">
-        <v>305.9545412000001</v>
+        <v>309.9279768000001</v>
       </c>
       <c r="N79">
-        <v>-31.15454120000004</v>
+        <v>-35.12797680000006</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-31.15454120000004</v>
+        <v>-35.12797680000006</v>
       </c>
       <c r="Q79">
-        <v>-21.45454120000005</v>
+        <v>-25.42797680000007</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2477591275552692</v>
+        <v>0.2569390878986906</v>
       </c>
       <c r="T79">
-        <v>3.936559302378637</v>
+        <v>4.115493816123121</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8981726465709343</v>
+        <v>0.8866576126405377</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1710305993377119</v>
+        <v>0.172040599337712</v>
       </c>
       <c r="C80">
-        <v>-477.6307522446277</v>
+        <v>-512.2261064943978</v>
       </c>
       <c r="D80">
-        <v>1313.495247755372</v>
+        <v>1305.966893505602</v>
       </c>
       <c r="E80">
-        <v>2111.226</v>
+        <v>2138.293</v>
       </c>
       <c r="F80">
-        <v>2111.226</v>
+        <v>2138.293</v>
       </c>
       <c r="G80">
         <v>320.1</v>
@@ -7847,28 +7847,28 @@
         <v>274.8</v>
       </c>
       <c r="M80">
-        <v>309.9279768000001</v>
+        <v>313.9014124</v>
       </c>
       <c r="N80">
-        <v>-35.12797680000006</v>
+        <v>-39.10141240000002</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-35.12797680000006</v>
+        <v>-39.10141240000002</v>
       </c>
       <c r="Q80">
-        <v>-25.42797680000007</v>
+        <v>-29.40141240000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2569390878986906</v>
+        <v>0.2669933301795807</v>
       </c>
       <c r="T80">
-        <v>4.115493816123121</v>
+        <v>4.311469712128985</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8866576126405377</v>
+        <v>0.8754340985564804</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.172040599337712</v>
+        <v>0.1730505993377119</v>
       </c>
       <c r="C81">
-        <v>-512.2261064943978</v>
+        <v>-546.7356543776132</v>
       </c>
       <c r="D81">
-        <v>1305.966893505602</v>
+        <v>1298.524345622387</v>
       </c>
       <c r="E81">
-        <v>2138.293</v>
+        <v>2165.36</v>
       </c>
       <c r="F81">
-        <v>2138.293</v>
+        <v>2165.36</v>
       </c>
       <c r="G81">
         <v>320.1</v>
@@ -7929,28 +7929,28 @@
         <v>274.8</v>
       </c>
       <c r="M81">
-        <v>313.9014124</v>
+        <v>317.874848</v>
       </c>
       <c r="N81">
-        <v>-39.10141240000002</v>
+        <v>-43.07484800000003</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-39.10141240000002</v>
+        <v>-43.07484800000003</v>
       </c>
       <c r="Q81">
-        <v>-29.40141240000003</v>
+        <v>-33.37484800000004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2669933301795807</v>
+        <v>0.2780529966885597</v>
       </c>
       <c r="T81">
-        <v>4.311469712128985</v>
+        <v>4.527043197735434</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8754340985564804</v>
+        <v>0.8644911723245243</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1730505993377119</v>
+        <v>0.174060599337712</v>
       </c>
       <c r="C82">
-        <v>-546.7356543776132</v>
+        <v>-581.1608545818058</v>
       </c>
       <c r="D82">
-        <v>1298.524345622387</v>
+        <v>1291.166145418194</v>
       </c>
       <c r="E82">
-        <v>2165.36</v>
+        <v>2192.427</v>
       </c>
       <c r="F82">
-        <v>2165.36</v>
+        <v>2192.427</v>
       </c>
       <c r="G82">
         <v>320.1</v>
@@ -8011,28 +8011,28 @@
         <v>274.8</v>
       </c>
       <c r="M82">
-        <v>317.874848</v>
+        <v>321.8482836000001</v>
       </c>
       <c r="N82">
-        <v>-43.07484800000003</v>
+        <v>-47.04828360000005</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-43.07484800000003</v>
+        <v>-47.04828360000005</v>
       </c>
       <c r="Q82">
-        <v>-33.37484800000004</v>
+        <v>-37.34828360000006</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2780529966885597</v>
+        <v>0.2902768386195365</v>
       </c>
       <c r="T82">
-        <v>4.527043197735434</v>
+        <v>4.765308629195194</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8644911723245243</v>
+        <v>0.8538184418019993</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.174060599337712</v>
+        <v>0.175070599337712</v>
       </c>
       <c r="C83">
-        <v>-581.1608545818058</v>
+        <v>-615.5031329176913</v>
       </c>
       <c r="D83">
-        <v>1291.166145418194</v>
+        <v>1283.890867082309</v>
       </c>
       <c r="E83">
-        <v>2192.427</v>
+        <v>2219.494</v>
       </c>
       <c r="F83">
-        <v>2192.427</v>
+        <v>2219.494</v>
       </c>
       <c r="G83">
         <v>320.1</v>
@@ -8093,28 +8093,28 @@
         <v>274.8</v>
       </c>
       <c r="M83">
-        <v>321.8482836000001</v>
+        <v>325.8217192000001</v>
       </c>
       <c r="N83">
-        <v>-47.04828360000005</v>
+        <v>-51.02171920000006</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-47.04828360000005</v>
+        <v>-51.02171920000006</v>
       </c>
       <c r="Q83">
-        <v>-37.34828360000006</v>
+        <v>-41.32171920000008</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2902768386195365</v>
+        <v>0.3038588852095108</v>
       </c>
       <c r="T83">
-        <v>4.765308629195194</v>
+        <v>5.030047997483816</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8538184418019993</v>
+        <v>0.8434060217800237</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.175070599337712</v>
+        <v>0.1760805993377119</v>
       </c>
       <c r="C84">
-        <v>-615.5031329176913</v>
+        <v>-649.7638832402272</v>
       </c>
       <c r="D84">
-        <v>1283.890867082309</v>
+        <v>1276.697116759773</v>
       </c>
       <c r="E84">
-        <v>2219.494</v>
+        <v>2246.561</v>
       </c>
       <c r="F84">
-        <v>2219.494</v>
+        <v>2246.561</v>
       </c>
       <c r="G84">
         <v>320.1</v>
@@ -8175,28 +8175,28 @@
         <v>274.8</v>
       </c>
       <c r="M84">
-        <v>325.8217192000001</v>
+        <v>329.7951548</v>
       </c>
       <c r="N84">
-        <v>-51.02171920000006</v>
+        <v>-54.99515480000002</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-51.02171920000006</v>
+        <v>-54.99515480000002</v>
       </c>
       <c r="Q84">
-        <v>-41.32171920000008</v>
+        <v>-45.29515480000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3038588852095108</v>
+        <v>0.3190388196335997</v>
       </c>
       <c r="T84">
-        <v>5.030047997483816</v>
+        <v>5.325933173806394</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8434060217800237</v>
+        <v>0.8332445034453246</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1760805993377119</v>
+        <v>0.1770905993377119</v>
       </c>
       <c r="C85">
-        <v>-649.7638832402272</v>
+        <v>-683.9444683388801</v>
       </c>
       <c r="D85">
-        <v>1276.697116759773</v>
+        <v>1269.58353166112</v>
       </c>
       <c r="E85">
-        <v>2246.561</v>
+        <v>2273.628</v>
       </c>
       <c r="F85">
-        <v>2246.561</v>
+        <v>2273.628</v>
       </c>
       <c r="G85">
         <v>320.1</v>
@@ -8257,28 +8257,28 @@
         <v>274.8</v>
       </c>
       <c r="M85">
-        <v>329.7951548</v>
+        <v>333.7685904000001</v>
       </c>
       <c r="N85">
-        <v>-54.99515480000002</v>
+        <v>-58.96859040000004</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-54.99515480000002</v>
+        <v>-58.96859040000004</v>
       </c>
       <c r="Q85">
-        <v>-45.29515480000003</v>
+        <v>-49.26859040000005</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3190388196335997</v>
+        <v>0.3361162458606997</v>
       </c>
       <c r="T85">
-        <v>5.325933173806394</v>
+        <v>5.658803997169294</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8332445034453246</v>
+        <v>0.8233249260233565</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1770905993377119</v>
+        <v>0.1781005993377119</v>
       </c>
       <c r="C86">
-        <v>-683.9444683388797</v>
+        <v>-718.0462207982937</v>
       </c>
       <c r="D86">
-        <v>1269.58353166112</v>
+        <v>1262.548779201706</v>
       </c>
       <c r="E86">
-        <v>2273.628</v>
+        <v>2300.695</v>
       </c>
       <c r="F86">
-        <v>2273.628</v>
+        <v>2300.695</v>
       </c>
       <c r="G86">
         <v>320.1</v>
@@ -8339,28 +8339,28 @@
         <v>274.8</v>
       </c>
       <c r="M86">
-        <v>333.7685904</v>
+        <v>337.742026</v>
       </c>
       <c r="N86">
-        <v>-58.96859039999998</v>
+        <v>-62.942026</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-58.96859039999998</v>
+        <v>-62.942026</v>
       </c>
       <c r="Q86">
-        <v>-49.26859039999999</v>
+        <v>-53.24202600000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3361162458606995</v>
+        <v>0.3554706622514128</v>
       </c>
       <c r="T86">
-        <v>5.658803997169291</v>
+        <v>6.036057596980577</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8233249260233566</v>
+        <v>0.8136387504230818</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1781005993377119</v>
+        <v>0.1791105993377119</v>
       </c>
       <c r="C87">
-        <v>-718.0462207982937</v>
+        <v>-752.0704438304992</v>
       </c>
       <c r="D87">
-        <v>1262.548779201706</v>
+        <v>1255.5915561695</v>
       </c>
       <c r="E87">
-        <v>2300.695</v>
+        <v>2327.762</v>
       </c>
       <c r="F87">
-        <v>2300.695</v>
+        <v>2327.762</v>
       </c>
       <c r="G87">
         <v>320.1</v>
@@ -8421,28 +8421,28 @@
         <v>274.8</v>
       </c>
       <c r="M87">
-        <v>337.742026</v>
+        <v>341.7154616</v>
       </c>
       <c r="N87">
-        <v>-62.942026</v>
+        <v>-66.91546159999996</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-62.942026</v>
+        <v>-66.91546159999996</v>
       </c>
       <c r="Q87">
-        <v>-53.24202600000001</v>
+        <v>-57.21546159999997</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3554706622514128</v>
+        <v>0.3775899952693709</v>
       </c>
       <c r="T87">
-        <v>6.036057596980577</v>
+        <v>6.467204568193475</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8136387504230818</v>
+        <v>0.804177834720488</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1791105993377119</v>
+        <v>0.2271005993377119</v>
       </c>
       <c r="C88">
-        <v>-752.0704438304992</v>
+        <v>-1039.671886240808</v>
       </c>
       <c r="D88">
-        <v>1255.5915561695</v>
+        <v>995.0571137591919</v>
       </c>
       <c r="E88">
-        <v>2327.762</v>
+        <v>2354.829</v>
       </c>
       <c r="F88">
-        <v>2327.762</v>
+        <v>2354.829</v>
       </c>
       <c r="G88">
         <v>320.1</v>
@@ -8503,45 +8503,45 @@
         <v>274.8</v>
       </c>
       <c r="M88">
-        <v>341.7154616</v>
+        <v>472.8496632</v>
       </c>
       <c r="N88">
-        <v>-66.91546159999996</v>
+        <v>-198.0496631999999</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-66.91546159999996</v>
+        <v>-198.0496631999999</v>
       </c>
       <c r="Q88">
-        <v>-57.21546159999997</v>
+        <v>-188.3496632</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3775899952693709</v>
+        <v>0.403112302597784</v>
       </c>
       <c r="T88">
-        <v>6.467204568193475</v>
+        <v>6.964681842669896</v>
       </c>
       <c r="U88">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
         <v>0</v>
       </c>
       <c r="W88">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.804177834720488</v>
+        <v>0.5811572290023364</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2271005993377119</v>
+        <v>0.2286505993377119</v>
       </c>
       <c r="C89">
-        <v>-1039.671886240808</v>
+        <v>-1073.363260009011</v>
       </c>
       <c r="D89">
-        <v>995.0571137591919</v>
+        <v>988.4327399909882</v>
       </c>
       <c r="E89">
-        <v>2354.829</v>
+        <v>2381.896</v>
       </c>
       <c r="F89">
-        <v>2354.829</v>
+        <v>2381.896</v>
       </c>
       <c r="G89">
         <v>320.1</v>
@@ -8585,28 +8585,28 @@
         <v>274.8</v>
       </c>
       <c r="M89">
-        <v>472.8496632</v>
+        <v>478.2847168</v>
       </c>
       <c r="N89">
-        <v>-198.0496631999999</v>
+        <v>-203.4847167999999</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-198.0496631999999</v>
+        <v>-203.4847167999999</v>
       </c>
       <c r="Q89">
-        <v>-188.3496632</v>
+        <v>-193.7847168</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.403112302597784</v>
+        <v>0.4328883278142661</v>
       </c>
       <c r="T89">
-        <v>6.964681842669896</v>
+        <v>7.545071996225722</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5811572290023364</v>
+        <v>0.5745531695818553</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2286505993377119</v>
+        <v>0.2302005993377119</v>
       </c>
       <c r="C90">
-        <v>-1073.363260009011</v>
+        <v>-1106.967016449018</v>
       </c>
       <c r="D90">
-        <v>988.4327399909882</v>
+        <v>981.8959835509814</v>
       </c>
       <c r="E90">
-        <v>2381.896</v>
+        <v>2408.963</v>
       </c>
       <c r="F90">
-        <v>2381.896</v>
+        <v>2408.963</v>
       </c>
       <c r="G90">
         <v>320.1</v>
@@ -8667,28 +8667,28 @@
         <v>274.8</v>
       </c>
       <c r="M90">
-        <v>478.2847168</v>
+        <v>483.7197704</v>
       </c>
       <c r="N90">
-        <v>-203.4847167999999</v>
+        <v>-208.9197703999999</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-203.4847167999999</v>
+        <v>-208.9197703999999</v>
       </c>
       <c r="Q90">
-        <v>-193.7847168</v>
+        <v>-199.2197704</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4328883278142661</v>
+        <v>0.4680781757973812</v>
       </c>
       <c r="T90">
-        <v>7.545071996225722</v>
+        <v>8.230987632246242</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5745531695818553</v>
+        <v>0.568097515991048</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2302005993377119</v>
+        <v>0.2317505993377119</v>
       </c>
       <c r="C91">
-        <v>-1106.967016449018</v>
+        <v>-1140.484882447339</v>
       </c>
       <c r="D91">
-        <v>981.8959835509814</v>
+        <v>975.4451175526602</v>
       </c>
       <c r="E91">
-        <v>2408.963</v>
+        <v>2436.03</v>
       </c>
       <c r="F91">
-        <v>2408.963</v>
+        <v>2436.03</v>
       </c>
       <c r="G91">
         <v>320.1</v>
@@ -8749,28 +8749,28 @@
         <v>274.8</v>
       </c>
       <c r="M91">
-        <v>483.7197704</v>
+        <v>489.154824</v>
       </c>
       <c r="N91">
-        <v>-208.9197703999999</v>
+        <v>-214.354824</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-208.9197703999999</v>
+        <v>-214.354824</v>
       </c>
       <c r="Q91">
-        <v>-199.2197704</v>
+        <v>-204.654824</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4680781757973812</v>
+        <v>0.5103059933771193</v>
       </c>
       <c r="T91">
-        <v>8.230987632246242</v>
+        <v>9.054086395470868</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.568097515991048</v>
+        <v>0.5617853213689252</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2317505993377119</v>
+        <v>0.2333005993377119</v>
       </c>
       <c r="C92">
-        <v>-1140.484882447339</v>
+        <v>-1173.918539805451</v>
       </c>
       <c r="D92">
-        <v>975.4451175526602</v>
+        <v>969.0784601945493</v>
       </c>
       <c r="E92">
-        <v>2436.03</v>
+        <v>2463.097</v>
       </c>
       <c r="F92">
-        <v>2436.03</v>
+        <v>2463.097</v>
       </c>
       <c r="G92">
         <v>320.1</v>
@@ -8831,28 +8831,28 @@
         <v>274.8</v>
       </c>
       <c r="M92">
-        <v>489.154824</v>
+        <v>494.5898776</v>
       </c>
       <c r="N92">
-        <v>-214.354824</v>
+        <v>-219.7898776</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-214.354824</v>
+        <v>-219.7898776</v>
       </c>
       <c r="Q92">
-        <v>-204.654824</v>
+        <v>-210.0898776</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5103059933771193</v>
+        <v>0.5619177704190216</v>
       </c>
       <c r="T92">
-        <v>9.054086395470868</v>
+        <v>10.06009599496763</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5617853213689252</v>
+        <v>0.5556118562989369</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2333005993377119</v>
+        <v>0.2348505993377119</v>
       </c>
       <c r="C93">
-        <v>-1173.918539805451</v>
+        <v>-1207.269626701582</v>
       </c>
       <c r="D93">
-        <v>969.0784601945493</v>
+        <v>962.7943732984178</v>
       </c>
       <c r="E93">
-        <v>2463.097</v>
+        <v>2490.164</v>
       </c>
       <c r="F93">
-        <v>2463.097</v>
+        <v>2490.164</v>
       </c>
       <c r="G93">
         <v>320.1</v>
@@ -8913,28 +8913,28 @@
         <v>274.8</v>
       </c>
       <c r="M93">
-        <v>494.5898776</v>
+        <v>500.0249312</v>
       </c>
       <c r="N93">
-        <v>-219.7898776</v>
+        <v>-225.2249312</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-219.7898776</v>
+        <v>-225.2249312</v>
       </c>
       <c r="Q93">
-        <v>-210.0898776</v>
+        <v>-215.5249312</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5619177704190216</v>
+        <v>0.6264324917213994</v>
       </c>
       <c r="T93">
-        <v>10.06009599496763</v>
+        <v>11.31760799433859</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5556118562989369</v>
+        <v>0.5495725969913399</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2348505993377119</v>
+        <v>0.236400599337712</v>
       </c>
       <c r="C94">
-        <v>-1207.269626701582</v>
+        <v>-1240.539739096005</v>
       </c>
       <c r="D94">
-        <v>962.7943732984178</v>
+        <v>956.5912609039949</v>
       </c>
       <c r="E94">
-        <v>2490.164</v>
+        <v>2517.231</v>
       </c>
       <c r="F94">
-        <v>2490.164</v>
+        <v>2517.231</v>
       </c>
       <c r="G94">
         <v>320.1</v>
@@ -8995,28 +8995,28 @@
         <v>274.8</v>
       </c>
       <c r="M94">
-        <v>500.0249312</v>
+        <v>505.4599848</v>
       </c>
       <c r="N94">
-        <v>-225.2249312</v>
+        <v>-230.6599848</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-225.2249312</v>
+        <v>-230.6599848</v>
       </c>
       <c r="Q94">
-        <v>-215.5249312</v>
+        <v>-220.9599848</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6264324917213994</v>
+        <v>0.7093799905387422</v>
       </c>
       <c r="T94">
-        <v>11.31760799433859</v>
+        <v>12.93440913638696</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5495725969913399</v>
+        <v>0.543663214227992</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.236400599337712</v>
+        <v>0.237950599337712</v>
       </c>
       <c r="C95">
-        <v>-1240.539739096005</v>
+        <v>-1273.730432082336</v>
       </c>
       <c r="D95">
-        <v>956.5912609039949</v>
+        <v>950.4675679176636</v>
       </c>
       <c r="E95">
-        <v>2517.231</v>
+        <v>2544.298</v>
       </c>
       <c r="F95">
-        <v>2517.231</v>
+        <v>2544.298</v>
       </c>
       <c r="G95">
         <v>320.1</v>
@@ -9077,28 +9077,28 @@
         <v>274.8</v>
       </c>
       <c r="M95">
-        <v>505.4599848</v>
+        <v>510.8950384</v>
       </c>
       <c r="N95">
-        <v>-230.6599848</v>
+        <v>-236.0950384</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-230.6599848</v>
+        <v>-236.0950384</v>
       </c>
       <c r="Q95">
-        <v>-220.9599848</v>
+        <v>-226.3950384</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7093799905387422</v>
+        <v>0.8199766556285328</v>
       </c>
       <c r="T95">
-        <v>12.93440913638696</v>
+        <v>15.09014399245146</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.543663214227992</v>
+        <v>0.5378795630128007</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.237950599337712</v>
+        <v>0.239500599337712</v>
       </c>
       <c r="C96">
-        <v>-1273.730432082336</v>
+        <v>-1306.843221187276</v>
       </c>
       <c r="D96">
-        <v>950.4675679176636</v>
+        <v>944.4217788127239</v>
       </c>
       <c r="E96">
-        <v>2544.298</v>
+        <v>2571.365</v>
       </c>
       <c r="F96">
-        <v>2544.298</v>
+        <v>2571.365</v>
       </c>
       <c r="G96">
         <v>320.1</v>
@@ -9159,28 +9159,28 @@
         <v>274.8</v>
       </c>
       <c r="M96">
-        <v>510.8950384</v>
+        <v>516.3300919999999</v>
       </c>
       <c r="N96">
-        <v>-236.0950384</v>
+        <v>-241.5300919999999</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-236.0950384</v>
+        <v>-241.5300919999999</v>
       </c>
       <c r="Q96">
-        <v>-226.3950384</v>
+        <v>-231.8300919999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8199766556285328</v>
+        <v>0.9748119867542399</v>
       </c>
       <c r="T96">
-        <v>15.09014399245146</v>
+        <v>18.10817279094176</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5378795630128007</v>
+        <v>0.5322176728758239</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.239500599337712</v>
+        <v>0.2410505993377119</v>
       </c>
       <c r="C97">
-        <v>-1306.843221187276</v>
+        <v>-1339.87958362105</v>
       </c>
       <c r="D97">
-        <v>944.4217788127239</v>
+        <v>938.4524163789499</v>
       </c>
       <c r="E97">
-        <v>2571.365</v>
+        <v>2598.432</v>
       </c>
       <c r="F97">
-        <v>2571.365</v>
+        <v>2598.432</v>
       </c>
       <c r="G97">
         <v>320.1</v>
@@ -9241,28 +9241,28 @@
         <v>274.8</v>
       </c>
       <c r="M97">
-        <v>516.3300919999999</v>
+        <v>521.7651456000001</v>
       </c>
       <c r="N97">
-        <v>-241.5300919999999</v>
+        <v>-246.9651456000001</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-241.5300919999999</v>
+        <v>-246.9651456000001</v>
       </c>
       <c r="Q97">
-        <v>-231.8300919999999</v>
+        <v>-237.2651456000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9748119867542399</v>
+        <v>1.2070649834428</v>
       </c>
       <c r="T97">
-        <v>18.10817279094176</v>
+        <v>22.63521598867721</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5322176728758239</v>
+        <v>0.5266737387833672</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2410505993377119</v>
+        <v>0.2426005993377119</v>
       </c>
       <c r="C98">
-        <v>-1339.87958362105</v>
+        <v>-1372.84095948073</v>
       </c>
       <c r="D98">
-        <v>938.4524163789499</v>
+        <v>932.5580405192701</v>
       </c>
       <c r="E98">
-        <v>2598.432</v>
+        <v>2625.499</v>
       </c>
       <c r="F98">
-        <v>2598.432</v>
+        <v>2625.499</v>
       </c>
       <c r="G98">
         <v>320.1</v>
@@ -9323,28 +9323,28 @@
         <v>274.8</v>
       </c>
       <c r="M98">
-        <v>521.7651456</v>
+        <v>527.2001991999999</v>
       </c>
       <c r="N98">
-        <v>-246.9651456</v>
+        <v>-252.4001991999999</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-246.9651456</v>
+        <v>-252.4001991999999</v>
       </c>
       <c r="Q98">
-        <v>-237.2651456</v>
+        <v>-242.7001991999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.207064983442797</v>
+        <v>1.594153311257063</v>
       </c>
       <c r="T98">
-        <v>22.63521598867715</v>
+        <v>30.18028798490286</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5266737387833673</v>
+        <v>0.521244112610343</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2426005993377119</v>
+        <v>0.2441505993377119</v>
       </c>
       <c r="C99">
-        <v>-1372.84095948073</v>
+        <v>-1405.728752908488</v>
       </c>
       <c r="D99">
-        <v>932.5580405192701</v>
+        <v>926.7372470915118</v>
       </c>
       <c r="E99">
-        <v>2625.499</v>
+        <v>2652.566</v>
       </c>
       <c r="F99">
-        <v>2625.499</v>
+        <v>2652.566</v>
       </c>
       <c r="G99">
         <v>320.1</v>
@@ -9405,28 +9405,28 @@
         <v>274.8</v>
       </c>
       <c r="M99">
-        <v>527.2001991999999</v>
+        <v>532.6352528</v>
       </c>
       <c r="N99">
-        <v>-252.4001991999999</v>
+        <v>-257.8352528</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-252.4001991999999</v>
+        <v>-257.8352528</v>
       </c>
       <c r="Q99">
-        <v>-242.7001991999999</v>
+        <v>-248.1352528</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.594153311257063</v>
+        <v>2.368329966885594</v>
       </c>
       <c r="T99">
-        <v>30.18028798490286</v>
+        <v>45.27043197735429</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.521244112610343</v>
+        <v>0.5159252951347272</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2441505993377119</v>
+        <v>0.2457005993377119</v>
       </c>
       <c r="C100">
-        <v>-1405.728752908488</v>
+        <v>-1438.544333206745</v>
       </c>
       <c r="D100">
-        <v>926.7372470915118</v>
+        <v>920.9886667932549</v>
       </c>
       <c r="E100">
-        <v>2652.566</v>
+        <v>2679.633</v>
       </c>
       <c r="F100">
-        <v>2652.566</v>
+        <v>2679.633</v>
       </c>
       <c r="G100">
         <v>320.1</v>
@@ -9487,28 +9487,28 @@
         <v>274.8</v>
       </c>
       <c r="M100">
-        <v>532.6352528</v>
+        <v>538.0703063999999</v>
       </c>
       <c r="N100">
-        <v>-257.8352528</v>
+        <v>-263.2703063999999</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-257.8352528</v>
+        <v>-263.2703063999999</v>
       </c>
       <c r="Q100">
-        <v>-248.1352528</v>
+        <v>-253.5703063999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.368329966885594</v>
+        <v>4.690859933771189</v>
       </c>
       <c r="T100">
-        <v>45.27043197735429</v>
+        <v>90.54086395470858</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5159252951347272</v>
+        <v>0.5107139285172047</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2457005993377119</v>
-      </c>
-      <c r="C101">
-        <v>-1438.544333206745</v>
-      </c>
-      <c r="D101">
-        <v>920.9886667932549</v>
-      </c>
-      <c r="E101">
-        <v>2679.633</v>
-      </c>
-      <c r="F101">
-        <v>2679.633</v>
-      </c>
-      <c r="G101">
-        <v>320.1</v>
-      </c>
-      <c r="H101">
-        <v>2706.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>284.5</v>
-      </c>
-      <c r="K101">
-        <v>9.699999999999989</v>
-      </c>
-      <c r="L101">
-        <v>274.8</v>
-      </c>
-      <c r="M101">
-        <v>538.0703063999999</v>
-      </c>
-      <c r="N101">
-        <v>-263.2703063999999</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-263.2703063999999</v>
-      </c>
-      <c r="Q101">
-        <v>-253.5703063999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.690859933771189</v>
-      </c>
-      <c r="T101">
-        <v>90.54086395470858</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2008</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5107139285172047</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
